--- a/mahkeme/2026-08-Dosya Listesi.xlsx
+++ b/mahkeme/2026-08-Dosya Listesi.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe_2026\26-yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3023E80-408A-40D2-B089-E5D4A78D441D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C5930B-AD31-4997-9990-C32328A0DE7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="915" yWindow="1770" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="hmb" sheetId="1" r:id="rId1"/>
-    <sheet name="AUB" sheetId="2" r:id="rId2"/>
-    <sheet name="ali" sheetId="3" r:id="rId3"/>
-    <sheet name="atila" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
-    <sheet name="Sayfa1" sheetId="6" r:id="rId6"/>
-    <sheet name="Sayfa5" sheetId="7" r:id="rId7"/>
+    <sheet name="Sayfa5" sheetId="7" r:id="rId1"/>
+    <sheet name="hmb" sheetId="1" r:id="rId2"/>
+    <sheet name="AUB" sheetId="2" r:id="rId3"/>
+    <sheet name="Sayfa2" sheetId="8" r:id="rId4"/>
+    <sheet name="ali" sheetId="3" r:id="rId5"/>
+    <sheet name="atila" sheetId="4" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId7"/>
+    <sheet name="Sayfa1" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="283">
   <si>
     <t>dava tarihi</t>
   </si>
@@ -929,9 +930,6 @@
     </r>
   </si>
   <si>
-    <t>hızlandırma dilekçesi</t>
-  </si>
-  <si>
     <t>kira tespit davası</t>
   </si>
   <si>
@@ -951,6 +949,48 @@
   </si>
   <si>
     <t>Örnek 13-icra – imzaya itiraz edildi</t>
+  </si>
+  <si>
+    <t>icr ahukuk</t>
+  </si>
+  <si>
+    <t>hızlandırma dilekçesi verildi</t>
+  </si>
+  <si>
+    <t>Tebligat yollandı</t>
+  </si>
+  <si>
+    <t>2sh samed turgut - örnek 13</t>
+  </si>
+  <si>
+    <t>2sh metin çelik - örnek 13</t>
+  </si>
+  <si>
+    <t>2025/269</t>
+  </si>
+  <si>
+    <t>1sh samed turgut - örnek 14</t>
+  </si>
+  <si>
+    <t>2sh ali demirel - örnek 14</t>
+  </si>
+  <si>
+    <t>İH-salih ant-ilamlı tahliye</t>
+  </si>
+  <si>
+    <t>Duruşma 1</t>
+  </si>
+  <si>
+    <t>2026/66</t>
+  </si>
+  <si>
+    <t>RTE-6. asliye ceza</t>
+  </si>
+  <si>
+    <t>6AC hmb-rte</t>
+  </si>
+  <si>
+    <t>4AH-hmb-maphre</t>
   </si>
 </sst>
 </file>
@@ -1556,7 +1596,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="167" fontId="26" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="267">
+  <cellXfs count="270">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
@@ -1962,6 +2002,9 @@
     <xf numFmtId="0" fontId="4" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2223,174 +2266,133 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:F20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="B2:E27"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="32.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <v>45902</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="10">
-        <v>45905</v>
-      </c>
-      <c r="F5" s="9">
-        <v>455688</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="11"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="12" t="s">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="269">
+        <v>46287</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>281</v>
+      </c>
+      <c r="D2" s="268">
+        <v>0.40625</v>
+      </c>
+      <c r="E2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" s="267">
+        <v>46288</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D3" s="268">
+        <v>0.37638888888888888</v>
+      </c>
+      <c r="E3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="267">
+        <v>46318</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>273</v>
+      </c>
+      <c r="E4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="267">
+        <v>46288</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="D5" s="268">
+        <v>0.375</v>
+      </c>
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="267">
+        <v>46289</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="D6" s="268">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="E6" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="269">
+        <v>46289</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="D7" s="268">
+        <v>0.40625</v>
+      </c>
+      <c r="E7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
-      <c r="C8" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="11"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>46044</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>46092</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D11" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="C12" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="11"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18">
-        <v>46177</v>
-      </c>
-      <c r="B13" s="19">
-        <v>0.41319444444444398</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="11"/>
-      <c r="F13" s="11"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D14" s="11"/>
-      <c r="F14" s="11"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D15" s="11"/>
-      <c r="F15" s="11"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
-        <v>45973</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="11"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="22"/>
-      <c r="D19" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" s="11"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="18">
-        <v>46132</v>
-      </c>
-      <c r="B20" s="23">
-        <v>0.42361111111111099</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="11"/>
+    </row>
+    <row r="8" spans="2:5" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8"/>
+      <c r="C8" s="2"/>
+      <c r="D8"/>
+      <c r="E8"/>
+    </row>
+    <row r="9" spans="2:5" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="267">
+        <v>46329</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>276</v>
+      </c>
+      <c r="D9" s="268">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="E9" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="2"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B27" s="11">
+        <v>45725</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -2403,8 +2405,210 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A3:F25"/>
+  <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>45902</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="10">
+        <v>45905</v>
+      </c>
+      <c r="F5" s="9">
+        <v>455688</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="11"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="14"/>
+      <c r="C8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="11"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>46044</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D11" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="C12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="11"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="18">
+        <v>46177</v>
+      </c>
+      <c r="B13" s="19">
+        <v>0.41319444444444398</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="F13" s="11"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D14" s="11"/>
+      <c r="F14" s="11"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D15" s="11"/>
+      <c r="F15" s="11"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>45973</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="10"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="11"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="22"/>
+      <c r="D19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="11"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="18">
+        <v>46132</v>
+      </c>
+      <c r="B20" s="23">
+        <v>0.42361111111111099</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="11"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="18">
+        <v>46287</v>
+      </c>
+      <c r="B25" s="23">
+        <v>0.40625</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>278</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Sayfa &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F170"/>
+  <dimension ref="A1:F174"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -2802,7 +3006,7 @@
       </c>
       <c r="B43" s="225"/>
       <c r="C43" s="258" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D43" s="5"/>
     </row>
@@ -2887,7 +3091,7 @@
       <c r="A51" s="259"/>
       <c r="B51" s="260"/>
       <c r="C51" s="262" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D51" s="50"/>
       <c r="F51" s="50"/>
@@ -2939,7 +3143,7 @@
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="225"/>
       <c r="C57" s="258" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D57" s="5"/>
     </row>
@@ -3006,497 +3210,505 @@
       </c>
       <c r="D64" s="5"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B65" s="3"/>
-      <c r="C65" s="13"/>
-      <c r="D65" s="5"/>
-    </row>
-    <row r="66" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="6">
+    <row r="65" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="248"/>
+      <c r="B65" s="249"/>
+      <c r="C65" s="250" t="s">
+        <v>271</v>
+      </c>
+      <c r="D65" s="50"/>
+    </row>
+    <row r="66" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="248"/>
+      <c r="B66" s="249"/>
+      <c r="C66" s="250"/>
+      <c r="D66" s="50"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B67" s="3"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="5"/>
+    </row>
+    <row r="68" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
         <v>45342</v>
       </c>
-      <c r="B66" s="228" t="s">
+      <c r="B68" s="228" t="s">
         <v>68</v>
       </c>
-      <c r="C66" s="21" t="s">
+      <c r="C68" s="21" t="s">
         <v>235</v>
       </c>
-      <c r="D66" s="9" t="s">
+      <c r="D68" s="9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B67" s="225"/>
-      <c r="C67" s="13" t="s">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B69" s="225"/>
+      <c r="C69" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D67" s="5"/>
-    </row>
-    <row r="68" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="39">
+      <c r="D69" s="5"/>
+    </row>
+    <row r="70" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A70" s="39">
         <v>45450</v>
       </c>
-      <c r="B68" s="229" t="s">
+      <c r="B70" s="229" t="s">
         <v>71</v>
       </c>
-      <c r="C68" s="34" t="s">
+      <c r="C70" s="34" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="69" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
+    <row r="71" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
         <v>45680</v>
       </c>
-      <c r="B69" s="229"/>
-      <c r="C69" s="242" t="s">
+      <c r="B71" s="229"/>
+      <c r="C71" s="242" t="s">
         <v>73</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="D71" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B70" s="225"/>
-      <c r="C70" s="34" t="s">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B72" s="225"/>
+      <c r="C72" s="34" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
         <v>45726</v>
       </c>
-      <c r="B71" s="230"/>
-      <c r="C71" s="2" t="s">
+      <c r="B73" s="230"/>
+      <c r="C73" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="219">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="219">
         <v>45765</v>
       </c>
-      <c r="B72" s="231" t="s">
+      <c r="B74" s="231" t="s">
         <v>257</v>
       </c>
-      <c r="C72" s="30" t="s">
+      <c r="C74" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="D72" s="5"/>
-      <c r="F72" s="5"/>
-    </row>
-    <row r="73" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="221">
+      <c r="D74" s="5"/>
+      <c r="F74" s="5"/>
+    </row>
+    <row r="75" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="221">
         <v>46195</v>
       </c>
-      <c r="B73" s="222" t="s">
+      <c r="B75" s="222" t="s">
         <v>256</v>
       </c>
-      <c r="C73" s="255" t="s">
+      <c r="C75" s="255" t="s">
         <v>259</v>
       </c>
-      <c r="D73" s="50"/>
-      <c r="F73" s="50"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="221"/>
-      <c r="B74" s="222"/>
-      <c r="C74" s="222" t="s">
+      <c r="D75" s="50"/>
+      <c r="F75" s="50"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="221"/>
+      <c r="B76" s="222"/>
+      <c r="C76" s="222" t="s">
         <v>243</v>
       </c>
-      <c r="D74" s="220"/>
-    </row>
-    <row r="75" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="33">
+      <c r="D76" s="220"/>
+    </row>
+    <row r="77" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="33">
         <v>46204</v>
       </c>
-      <c r="B75" s="34" t="s">
+      <c r="B77" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="C75" s="34" t="s">
+      <c r="C77" s="34" t="s">
         <v>260</v>
       </c>
-      <c r="D75" s="50"/>
-    </row>
-    <row r="76" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="33"/>
-      <c r="B76" s="34"/>
-      <c r="C76" s="254" t="s">
-        <v>262</v>
-      </c>
-      <c r="D76" s="50"/>
-    </row>
-    <row r="77" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="33"/>
-      <c r="B77" s="34"/>
-      <c r="C77" s="254" t="s">
-        <v>263</v>
-      </c>
       <c r="D77" s="50"/>
     </row>
     <row r="78" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="33"/>
-      <c r="B78" s="34"/>
-      <c r="C78" s="22" t="s">
-        <v>264</v>
+      <c r="A78" s="33">
+        <v>46220</v>
       </c>
       <c r="D78" s="50"/>
     </row>
-    <row r="79" spans="1:6" s="51" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="33"/>
-      <c r="B79" s="34"/>
-      <c r="C79" s="256" t="s">
-        <v>265</v>
+    <row r="79" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="33">
+        <v>46329</v>
+      </c>
+      <c r="B79" s="23">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="C79" s="20" t="s">
+        <v>44</v>
       </c>
       <c r="D79" s="50"/>
     </row>
     <row r="80" spans="1:6" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="33"/>
       <c r="B80" s="34"/>
-      <c r="C80" s="257" t="s">
-        <v>266</v>
+      <c r="C80" s="254" t="s">
+        <v>270</v>
       </c>
       <c r="D80" s="50"/>
     </row>
     <row r="81" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="33"/>
       <c r="B81" s="34"/>
-      <c r="C81" s="254"/>
+      <c r="C81" s="254" t="s">
+        <v>262</v>
+      </c>
       <c r="D81" s="50"/>
     </row>
     <row r="82" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="33"/>
       <c r="B82" s="34"/>
-      <c r="C82" s="254"/>
+      <c r="C82" s="22" t="s">
+        <v>263</v>
+      </c>
       <c r="D82" s="50"/>
     </row>
-    <row r="83" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" s="51" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="33"/>
       <c r="B83" s="34"/>
-      <c r="C83" s="254"/>
+      <c r="C83" s="256" t="s">
+        <v>264</v>
+      </c>
       <c r="D83" s="50"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B84" s="3"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="5"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="40">
-        <v>46076</v>
-      </c>
-      <c r="B85" s="41" t="s">
-        <v>75</v>
-      </c>
-      <c r="C85" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="D85" s="20">
-        <v>515608</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="40"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="D86" s="42">
-        <v>46088</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="40">
-        <v>46120</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D87" s="43"/>
+    <row r="84" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="33"/>
+      <c r="B84" s="34"/>
+      <c r="C84" s="257" t="s">
+        <v>265</v>
+      </c>
+      <c r="D84" s="50"/>
+    </row>
+    <row r="85" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="33"/>
+      <c r="B85" s="34"/>
+      <c r="C85" s="254"/>
+      <c r="D85" s="50"/>
+    </row>
+    <row r="86" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="33"/>
+      <c r="B86" s="34"/>
+      <c r="C86" s="254"/>
+      <c r="D86" s="50"/>
+    </row>
+    <row r="87" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="33"/>
+      <c r="B87" s="34"/>
+      <c r="C87" s="254"/>
+      <c r="D87" s="50"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="40">
-        <v>46121</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D88" s="43"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="5"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="40">
-        <v>46120</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D89" s="43"/>
+        <v>46076</v>
+      </c>
+      <c r="B89" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="C89" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="D89" s="20">
+        <v>515608</v>
+      </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="40">
-        <v>46121</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D90" s="43"/>
+      <c r="A90" s="40"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="D90" s="42">
+        <v>46088</v>
+      </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="40">
-        <v>46121</v>
-      </c>
-      <c r="B91" s="3"/>
+        <v>46120</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="C91" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D91" s="43"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="40">
-        <v>46122</v>
-      </c>
-      <c r="B92" s="3"/>
+        <v>46121</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="C92" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D92" s="43"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="40"/>
-      <c r="B93" s="3"/>
+      <c r="A93" s="40">
+        <v>46120</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="C93" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D93" s="43"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="40"/>
-      <c r="B94" s="3"/>
+      <c r="A94" s="40">
+        <v>46121</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="C94" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D94" s="43"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="40"/>
+      <c r="A95" s="40">
+        <v>46121</v>
+      </c>
       <c r="B95" s="3"/>
       <c r="C95" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D95" s="43"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="40">
+        <v>46122</v>
+      </c>
+      <c r="B96" s="3"/>
+      <c r="C96" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D96" s="43"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="40"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D97" s="43"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="40"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D98" s="43"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="40"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D95" s="43"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="40"/>
-      <c r="B96" s="30"/>
-      <c r="C96" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="D96" s="43"/>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="40">
-        <v>46122</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="40">
-        <v>46122</v>
-      </c>
-      <c r="B98" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D98" s="48" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="40">
-        <v>46127</v>
-      </c>
-      <c r="B99" s="3"/>
-      <c r="C99" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="D99" s="44">
-        <v>375000</v>
-      </c>
+      <c r="D99" s="43"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="40"/>
-      <c r="B100" s="3"/>
-      <c r="C100" s="28" t="s">
+      <c r="B100" s="30"/>
+      <c r="C100" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="D100" s="43"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="40">
+        <v>46122</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="40">
+        <v>46122</v>
+      </c>
+      <c r="B102" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D102" s="48" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="40">
+        <v>46127</v>
+      </c>
+      <c r="B103" s="3"/>
+      <c r="C103" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="D103" s="44">
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="40"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="D100" s="43"/>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="40"/>
-      <c r="B101" s="3"/>
-      <c r="C101" s="2" t="s">
+      <c r="D104" s="43"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="40"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D101" s="43"/>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="43"/>
-      <c r="B102" s="251"/>
-      <c r="C102" s="251" t="s">
-        <v>94</v>
-      </c>
-      <c r="D102" s="43"/>
-    </row>
-    <row r="103" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="40">
-        <v>46206</v>
-      </c>
-      <c r="B103" s="251"/>
-      <c r="C103" s="252" t="s">
-        <v>244</v>
-      </c>
-      <c r="D103" s="43"/>
-    </row>
-    <row r="104" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="40">
-        <v>46126</v>
-      </c>
-      <c r="B104" s="251"/>
-      <c r="C104" s="252" t="s">
-        <v>252</v>
-      </c>
-      <c r="D104" s="43"/>
-    </row>
-    <row r="105" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="40">
-        <v>46217</v>
-      </c>
-      <c r="B105" s="251"/>
-      <c r="C105" s="252" t="s">
-        <v>245</v>
-      </c>
       <c r="D105" s="43"/>
     </row>
-    <row r="106" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="43"/>
       <c r="B106" s="251"/>
-      <c r="C106" s="252" t="s">
+      <c r="C106" s="251" t="s">
+        <v>94</v>
+      </c>
+      <c r="D106" s="43"/>
+    </row>
+    <row r="107" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="40">
+        <v>46206</v>
+      </c>
+      <c r="B107" s="251"/>
+      <c r="C107" s="252" t="s">
+        <v>244</v>
+      </c>
+      <c r="D107" s="43"/>
+    </row>
+    <row r="108" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="40">
+        <v>46126</v>
+      </c>
+      <c r="B108" s="251"/>
+      <c r="C108" s="252" t="s">
+        <v>252</v>
+      </c>
+      <c r="D108" s="43"/>
+    </row>
+    <row r="109" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="40">
+        <v>46217</v>
+      </c>
+      <c r="B109" s="251"/>
+      <c r="C109" s="252" t="s">
+        <v>245</v>
+      </c>
+      <c r="D109" s="43"/>
+    </row>
+    <row r="110" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="43"/>
+      <c r="B110" s="251"/>
+      <c r="C110" s="252" t="s">
         <v>246</v>
       </c>
-      <c r="D106" s="43"/>
-    </row>
-    <row r="107" spans="1:4" s="243" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="253"/>
-      <c r="B107" s="263" t="s">
+      <c r="D110" s="43"/>
+    </row>
+    <row r="111" spans="1:4" s="243" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="253"/>
+      <c r="B111" s="263" t="s">
         <v>247</v>
       </c>
-      <c r="C107" s="244" t="s">
+      <c r="C111" s="244" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" s="243" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="253"/>
-      <c r="C108" s="244" t="s">
+      <c r="D111" s="243" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" s="243" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="253"/>
+      <c r="C112" s="244" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="109" spans="1:4" s="243" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="253"/>
-      <c r="C109" s="244"/>
-    </row>
-    <row r="110" spans="1:4" s="243" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="38">
+    <row r="113" spans="1:4" s="243" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="253"/>
+      <c r="C113" s="244"/>
+    </row>
+    <row r="114" spans="1:4" s="243" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="38">
         <v>46289</v>
       </c>
-      <c r="B110" s="23">
+      <c r="B114" s="23">
         <v>0.39583333333333331</v>
       </c>
-      <c r="C110" s="244" t="s">
+      <c r="C114" s="244" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B111" s="3"/>
-      <c r="C111" s="13"/>
-      <c r="D111" s="5"/>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="40">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B115" s="3"/>
+      <c r="C115" s="13"/>
+      <c r="D115" s="5"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="40">
         <v>45676</v>
       </c>
-      <c r="B112" s="45" t="s">
+      <c r="B116" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="C112" s="41" t="s">
+      <c r="C116" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="D112" s="47"/>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="46">
+      <c r="D116" s="47"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="46">
         <v>45698</v>
       </c>
-      <c r="B113" s="3"/>
-      <c r="C113" s="28" t="s">
+      <c r="B117" s="3"/>
+      <c r="C117" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="D113" s="47"/>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="40"/>
-      <c r="B114" s="45"/>
-      <c r="C114" s="20" t="s">
+      <c r="D117" s="47"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="40"/>
+      <c r="B118" s="45"/>
+      <c r="C118" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="D114" s="241" t="s">
+      <c r="D118" s="241" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="264"/>
-      <c r="B115" s="265"/>
-      <c r="C115" s="261"/>
-      <c r="D115" s="266"/>
-    </row>
-    <row r="116" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="264"/>
-      <c r="B116" s="265"/>
-      <c r="C116" s="262" t="s">
-        <v>268</v>
-      </c>
-      <c r="D116" s="266"/>
-    </row>
-    <row r="117" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="264"/>
-      <c r="B117" s="265"/>
-      <c r="C117" s="261"/>
-      <c r="D117" s="266"/>
-    </row>
-    <row r="118" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="264"/>
-      <c r="B118" s="265"/>
-      <c r="C118" s="261"/>
-      <c r="D118" s="266"/>
     </row>
     <row r="119" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="264"/>
@@ -3505,169 +3717,155 @@
       <c r="D119" s="266"/>
     </row>
     <row r="120" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="33"/>
-      <c r="B120" s="34"/>
-      <c r="C120" s="49"/>
-      <c r="D120" s="50"/>
+      <c r="A120" s="264"/>
+      <c r="B120" s="265"/>
+      <c r="C120" s="262" t="s">
+        <v>267</v>
+      </c>
+      <c r="D120" s="266"/>
     </row>
     <row r="121" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="40">
+      <c r="A121" s="264"/>
+      <c r="B121" s="265"/>
+      <c r="C121" s="261"/>
+      <c r="D121" s="266"/>
+    </row>
+    <row r="122" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="264"/>
+      <c r="B122" s="265"/>
+      <c r="C122" s="261"/>
+      <c r="D122" s="266"/>
+    </row>
+    <row r="123" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="264"/>
+      <c r="B123" s="265"/>
+      <c r="C123" s="261"/>
+      <c r="D123" s="266"/>
+    </row>
+    <row r="124" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="33"/>
+      <c r="B124" s="34"/>
+      <c r="C124" s="49"/>
+      <c r="D124" s="50"/>
+    </row>
+    <row r="125" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="40">
         <v>46205</v>
       </c>
-      <c r="B121" s="45" t="s">
+      <c r="B125" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="C121" s="41" t="s">
+      <c r="C125" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="D121" s="47"/>
-    </row>
-    <row r="122" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="46">
+      <c r="D125" s="47"/>
+    </row>
+    <row r="126" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="46">
         <v>45482</v>
       </c>
-      <c r="B122" s="3"/>
-      <c r="C122" s="28" t="s">
+      <c r="B126" s="3"/>
+      <c r="C126" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="D122" s="47"/>
-    </row>
-    <row r="123" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="40">
+      <c r="D126" s="47"/>
+    </row>
+    <row r="127" spans="1:4" s="51" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="40">
         <v>45672</v>
       </c>
-      <c r="B123" s="45"/>
-      <c r="C123" s="41"/>
-      <c r="D123" s="241" t="s">
+      <c r="B127" s="45"/>
+      <c r="C127" s="41"/>
+      <c r="D127" s="241" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B124" s="3"/>
-      <c r="C124" s="13"/>
-      <c r="D124" s="5"/>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="52">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B128" s="3"/>
+      <c r="C128" s="13"/>
+      <c r="D128" s="5"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="52">
         <v>45588</v>
       </c>
-      <c r="B125" s="53" t="s">
+      <c r="B129" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="C125" s="54" t="s">
+      <c r="C129" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="D125" s="241" t="s">
+      <c r="D129" s="241" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="52"/>
-      <c r="B126" s="53"/>
-      <c r="C126" s="54" t="s">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="52"/>
+      <c r="B130" s="53"/>
+      <c r="C130" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="D126" s="55"/>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="56">
-        <v>45438</v>
-      </c>
-      <c r="B127" s="57" t="s">
-        <v>104</v>
-      </c>
-      <c r="C127" s="58" t="s">
-        <v>105</v>
-      </c>
-      <c r="D127" s="48" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="56"/>
-      <c r="B128" s="57"/>
-      <c r="C128" s="58" t="s">
-        <v>106</v>
-      </c>
-      <c r="D128" s="47">
-        <v>193500</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="56">
-        <v>45288</v>
-      </c>
-      <c r="B129" s="60" t="s">
-        <v>108</v>
-      </c>
-      <c r="C129" s="61" t="s">
-        <v>109</v>
-      </c>
-      <c r="D129" s="61" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" s="56"/>
-      <c r="B130" s="60"/>
-      <c r="C130" s="61" t="s">
-        <v>103</v>
-      </c>
-      <c r="D130" s="59"/>
+      <c r="D130" s="55"/>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="56">
-        <v>45148</v>
-      </c>
-      <c r="B131" s="60" t="s">
-        <v>110</v>
-      </c>
-      <c r="C131" s="61" t="s">
-        <v>111</v>
-      </c>
-      <c r="D131" s="62" t="s">
-        <v>112</v>
+        <v>45438</v>
+      </c>
+      <c r="B131" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="C131" s="58" t="s">
+        <v>105</v>
+      </c>
+      <c r="D131" s="48" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="56"/>
-      <c r="B132" s="60"/>
-      <c r="C132" s="61"/>
-      <c r="D132" s="59"/>
+      <c r="B132" s="57"/>
+      <c r="C132" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="D132" s="47">
+        <v>193500</v>
+      </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="56">
-        <v>44928</v>
+        <v>45288</v>
       </c>
       <c r="B133" s="60" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C133" s="61" t="s">
-        <v>105</v>
-      </c>
-      <c r="D133" s="47">
-        <v>24316</v>
+        <v>109</v>
+      </c>
+      <c r="D133" s="61" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="56"/>
       <c r="B134" s="60"/>
-      <c r="C134" s="61"/>
-      <c r="D134" s="48" t="s">
-        <v>107</v>
-      </c>
+      <c r="C134" s="61" t="s">
+        <v>103</v>
+      </c>
+      <c r="D134" s="59"/>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="56">
-        <v>44333</v>
+        <v>45148</v>
       </c>
       <c r="B135" s="60" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C135" s="61" t="s">
-        <v>115</v>
-      </c>
-      <c r="D135" s="47"/>
+        <v>111</v>
+      </c>
+      <c r="D135" s="62" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="56"/>
@@ -3676,60 +3874,100 @@
       <c r="D136" s="59"/>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B137" s="3"/>
-      <c r="D137" s="5"/>
+      <c r="A137" s="56">
+        <v>44928</v>
+      </c>
+      <c r="B137" s="60" t="s">
+        <v>113</v>
+      </c>
+      <c r="C137" s="61" t="s">
+        <v>105</v>
+      </c>
+      <c r="D137" s="47">
+        <v>24316</v>
+      </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138"/>
-      <c r="B138"/>
-      <c r="C138"/>
+      <c r="A138" s="56"/>
+      <c r="B138" s="60"/>
+      <c r="C138" s="61"/>
+      <c r="D138" s="48" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139"/>
-      <c r="B139"/>
-      <c r="C139"/>
+      <c r="A139" s="56">
+        <v>44333</v>
+      </c>
+      <c r="B139" s="60" t="s">
+        <v>114</v>
+      </c>
+      <c r="C139" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="D139" s="47"/>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A140"/>
-      <c r="B140"/>
-      <c r="C140"/>
+      <c r="A140" s="56"/>
+      <c r="B140" s="60"/>
+      <c r="C140" s="61"/>
+      <c r="D140" s="59"/>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B141" s="3"/>
       <c r="D141" s="5"/>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B142" s="3"/>
-      <c r="D142" s="5"/>
+      <c r="A142"/>
+      <c r="B142"/>
+      <c r="C142"/>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B143" s="3"/>
-      <c r="D143" s="5"/>
+      <c r="A143"/>
+      <c r="B143"/>
+      <c r="C143"/>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B144" s="3"/>
-      <c r="D144" s="5"/>
+      <c r="A144"/>
+      <c r="B144"/>
+      <c r="C144"/>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A145" s="2"/>
+      <c r="B145" s="3"/>
+      <c r="D145" s="5"/>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B146" s="3"/>
+      <c r="D146" s="5"/>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B147" s="3"/>
+      <c r="D147" s="5"/>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D148" s="2"/>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D154" s="2"/>
-    </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B167" s="2"/>
-    </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B168" s="2"/>
-    </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B169" s="2"/>
-    </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B170" s="2"/>
+      <c r="B148" s="3"/>
+      <c r="D148" s="5"/>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" s="2"/>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D152" s="2"/>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D158" s="2"/>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B171" s="2"/>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B172" s="2"/>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B173" s="2"/>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B174" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -3741,7 +3979,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{454E653D-BDD8-4FC2-BBCC-47F6A1D2BE83}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A3:F14"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3841,7 +4088,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:F18"/>
   <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3955,7 +4202,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J119"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5672,7 +5919,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A4:G15"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5767,48 +6014,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B9:D13"/>
-  <sheetFormatPr defaultColWidth="10.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="32.7109375" style="2" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="2"/>
-      <c r="C11" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="11">
-        <v>45725</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Sayfa &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>
--- a/mahkeme/2026-08-Dosya Listesi.xlsx
+++ b/mahkeme/2026-08-Dosya Listesi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe_2026\26-yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C5930B-AD31-4997-9990-C32328A0DE7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3584BA5-52F5-43AC-852C-F7765F2DBE7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa5" sheetId="7" r:id="rId1"/>

--- a/mahkeme/2026-08-Dosya Listesi.xlsx
+++ b/mahkeme/2026-08-Dosya Listesi.xlsx
@@ -337,10 +337,10 @@
     <t xml:space="preserve">istinafa gidebilir</t>
   </si>
   <si>
-    <t xml:space="preserve">3 eylül istinaf için son gün istinafa gitmezse tahliye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">işlemleri başalayacak</t>
+    <t xml:space="preserve">1 eylül istinaf için son gün istinafa gitmezse tahliye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">işlemleri başalayacak. 2 eylül de itiraz edilemez.</t>
   </si>
   <si>
     <t xml:space="preserve">hhesaplarına haciz kondu çıkış için zorlanacak</t>
@@ -1116,13 +1116,11 @@
       <charset val="162"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-    </font>
-    <font>
+      <b val="true"/>
+      <i val="true"/>
       <u val="double"/>
       <sz val="11"/>
+      <color rgb="FFC9211E"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1133,6 +1131,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="162"/>
+    </font>
+    <font>
+      <u val="double"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1579,7 +1584,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="257">
+  <cellXfs count="244">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1592,11 +1597,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1728,14 +1729,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1796,22 +1789,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="168" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1824,11 +1805,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1836,7 +1817,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1880,11 +1861,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1900,7 +1881,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1908,31 +1889,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2108,10 +2069,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2601,10 +2558,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2674,7 +2627,7 @@
       <rgbColor rgb="FFC9211E"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF385724"/>
+      <rgbColor rgb="FF385623"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -2873,12 +2826,12 @@
       <c r="D2" s="3" t="n">
         <v>0.40625</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="2" t="n">
         <v>46288</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -2887,23 +2840,23 @@
       <c r="D3" s="3" t="n">
         <v>0.376388888888889</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="2" t="n">
         <v>46318</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="2" t="n">
         <v>46288</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -2912,12 +2865,12 @@
       <c r="D5" s="3" t="n">
         <v>0.375</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="2" t="n">
         <v>46289</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -2926,7 +2879,7 @@
       <c r="D6" s="3" t="n">
         <v>0.395833333333333</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2940,12 +2893,12 @@
       <c r="D7" s="3" t="n">
         <v>0.40625</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="2" t="n">
         <v>46329</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -2954,7 +2907,7 @@
       <c r="D9" s="3" t="n">
         <v>0.420138888888889</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2968,7 +2921,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="4" t="n">
         <v>45725</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -2997,43 +2950,43 @@
   <dimension ref="A3:F25"/>
   <sheetFormatPr defaultColWidth="10.14453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="10.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.57"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="9" t="n">
         <v>45902</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="14" t="n">
+      <c r="D5" s="12"/>
+      <c r="E5" s="13" t="n">
         <v>45905</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="12" t="n">
         <v>455688</v>
       </c>
     </row>
@@ -3041,129 +2994,129 @@
       <c r="C6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17"/>
-      <c r="C8" s="17" t="s">
+      <c r="A8" s="16"/>
+      <c r="C8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="5"/>
+      <c r="D8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="5" t="n">
         <v>46044</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="5" t="n">
         <v>46092</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="17" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="18" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20"/>
-      <c r="C12" s="19" t="s">
+      <c r="A12" s="19"/>
+      <c r="C12" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="5"/>
+      <c r="D12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="20" t="n">
         <v>46177</v>
       </c>
-      <c r="B13" s="22" t="n">
+      <c r="B13" s="21" t="n">
         <v>0.413194444444444</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="F13" s="5"/>
+      <c r="D13" s="4"/>
+      <c r="F13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="D14" s="4"/>
+      <c r="F14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="D15" s="4"/>
+      <c r="F15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="9" t="n">
         <v>45973</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="14"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7"/>
-      <c r="C18" s="7" t="s">
+      <c r="B18" s="6"/>
+      <c r="C18" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="5"/>
+      <c r="F18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="25"/>
-      <c r="D19" s="18" t="s">
+      <c r="B19" s="24"/>
+      <c r="D19" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="F19" s="5"/>
+      <c r="F19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="20" t="n">
         <v>46132</v>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="25" t="n">
         <v>0.423611111111111</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="5"/>
+      <c r="F20" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="5" t="n">
         <v>46127</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -3174,13 +3127,13 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21" t="n">
+      <c r="A25" s="20" t="n">
         <v>46287</v>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="25" t="n">
         <v>0.40625</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="22" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3203,10 +3156,10 @@
   <dimension ref="A1:F181"/>
   <sheetFormatPr defaultColWidth="10.14453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="11.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="11.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="48.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3215,7 +3168,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="28" t="n">
+      <c r="B2" s="27" t="n">
         <v>45725</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -3223,692 +3176,691 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="9"/>
+      <c r="E3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7"/>
-      <c r="C4" s="0"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
+      <c r="B4" s="6"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="29"/>
-      <c r="B5" s="30"/>
-      <c r="C5" s="31" t="s">
+      <c r="A5" s="28"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D8" s="9"/>
+      <c r="D8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="9" t="n">
         <v>45959</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="32" t="n">
+      <c r="D9" s="31" t="n">
         <v>196170</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="12" t="s">
+      <c r="A10" s="9"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="32"/>
+      <c r="D10" s="31"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33" t="n">
+      <c r="A11" s="32" t="n">
         <v>46009</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="34" t="s">
+      <c r="B11" s="6"/>
+      <c r="C11" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="9"/>
+      <c r="D11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="29"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="31" t="s">
+      <c r="A12" s="28"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="9"/>
+      <c r="D12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7"/>
-      <c r="D13" s="9"/>
+      <c r="B13" s="6"/>
+      <c r="D13" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="7"/>
-      <c r="D15" s="9"/>
+      <c r="B15" s="6"/>
+      <c r="D15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="9" t="n">
         <v>45475</v>
       </c>
-      <c r="B16" s="35" t="s">
+      <c r="B16" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="32" t="n">
+      <c r="D16" s="31" t="n">
         <v>74000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="36" t="s">
+      <c r="A17" s="9"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="32"/>
+      <c r="D17" s="31"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="33" t="n">
+      <c r="A18" s="32" t="n">
         <v>45482</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="37" t="s">
+      <c r="B18" s="34"/>
+      <c r="C18" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="38"/>
+      <c r="D18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="n">
+      <c r="A19" s="9" t="n">
         <v>45604</v>
       </c>
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="32" t="n">
+      <c r="D19" s="31" t="n">
         <v>140835</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10"/>
-      <c r="B20" s="35"/>
-      <c r="C20" s="12" t="s">
+      <c r="A20" s="9"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="32"/>
+      <c r="D20" s="31"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="33" t="n">
+      <c r="A21" s="32" t="n">
         <v>45615</v>
       </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="37" t="s">
+      <c r="B21" s="34"/>
+      <c r="C21" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="38"/>
+      <c r="D21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="5" t="n">
         <v>45704</v>
       </c>
-      <c r="B22" s="39" t="s">
+      <c r="B22" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="9"/>
+      <c r="D22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="7"/>
+      <c r="B23" s="6"/>
       <c r="C23" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="9"/>
+      <c r="D23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="5" t="n">
         <v>45989</v>
       </c>
-      <c r="B24" s="7"/>
+      <c r="B24" s="6"/>
       <c r="C24" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D24" s="9"/>
+      <c r="D24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="5" t="n">
         <v>46042</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="16" t="s">
+      <c r="B25" s="6"/>
+      <c r="C25" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="9"/>
+      <c r="D25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="n">
+      <c r="A26" s="5" t="n">
         <v>46155</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="16" t="s">
+      <c r="B26" s="6"/>
+      <c r="C26" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="9"/>
+      <c r="D26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="5" t="n">
         <v>46204</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="31" t="s">
+      <c r="B27" s="6"/>
+      <c r="C27" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="9"/>
+      <c r="D27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21" t="n">
+      <c r="A28" s="20" t="n">
         <v>46288</v>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="25" t="n">
         <v>0.376388888888889</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D28" s="9"/>
-      <c r="F28" s="9"/>
+      <c r="D28" s="8"/>
+      <c r="F28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="7"/>
-      <c r="D29" s="9"/>
-      <c r="F29" s="9"/>
+      <c r="B29" s="6"/>
+      <c r="D29" s="8"/>
+      <c r="F29" s="8"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="n">
+      <c r="A30" s="9" t="n">
         <v>45603</v>
       </c>
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D30" s="32"/>
+      <c r="D30" s="31"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10"/>
-      <c r="B31" s="35"/>
-      <c r="C31" s="40" t="s">
+      <c r="A31" s="9"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="D31" s="32"/>
+      <c r="D31" s="31"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="33" t="n">
+      <c r="A32" s="32" t="n">
         <v>45615</v>
       </c>
-      <c r="B32" s="35"/>
-      <c r="C32" s="34" t="s">
+      <c r="B32" s="34"/>
+      <c r="C32" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="8" t="n">
         <v>156000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="n">
+      <c r="A33" s="5" t="n">
         <v>45704</v>
       </c>
-      <c r="B33" s="39" t="s">
+      <c r="B33" s="36" t="s">
         <v>5</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D33" s="8" t="n">
+      <c r="D33" s="7" t="n">
         <v>86000</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="7"/>
+      <c r="B34" s="6"/>
       <c r="C34" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="41" t="s">
+      <c r="D34" s="38" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="n">
+      <c r="A35" s="5" t="n">
         <v>46086</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="6" t="s">
         <v>63</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D35" s="9"/>
+      <c r="D35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="7"/>
+      <c r="B36" s="6"/>
       <c r="C36" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D36" s="9"/>
+      <c r="D36" s="8"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="7"/>
+      <c r="B37" s="6"/>
       <c r="C37" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D37" s="9"/>
+      <c r="D37" s="8"/>
     </row>
     <row r="38" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="42" t="n">
+      <c r="A38" s="39" t="n">
         <v>46196</v>
       </c>
-      <c r="B38" s="43" t="n">
+      <c r="B38" s="40" t="n">
         <v>0.413194444444444</v>
       </c>
-      <c r="C38" s="44" t="s">
+      <c r="C38" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="D38" s="9"/>
-      <c r="F38" s="9"/>
+      <c r="D38" s="8"/>
+      <c r="F38" s="8"/>
     </row>
     <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="45" t="n">
+      <c r="A39" s="42" t="n">
         <v>46318</v>
       </c>
-      <c r="B39" s="46"/>
-      <c r="C39" s="47" t="s">
+      <c r="B39" s="43"/>
+      <c r="C39" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="D39" s="9"/>
-      <c r="F39" s="9"/>
+      <c r="D39" s="8"/>
+      <c r="F39" s="8"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="42"/>
-      <c r="B40" s="43"/>
-      <c r="C40" s="48"/>
-      <c r="D40" s="9"/>
-      <c r="F40" s="9"/>
+      <c r="A40" s="39"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="45"/>
+      <c r="D40" s="8"/>
+      <c r="F40" s="8"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="7"/>
-      <c r="D41" s="9"/>
+      <c r="B41" s="6"/>
+      <c r="D41" s="8"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="10" t="n">
+      <c r="A42" s="9" t="n">
         <v>45588</v>
       </c>
-      <c r="B42" s="35" t="s">
+      <c r="B42" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D42" s="32"/>
+      <c r="D42" s="31"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="33" t="n">
+      <c r="A43" s="32" t="n">
         <v>45596</v>
       </c>
-      <c r="B43" s="35"/>
-      <c r="C43" s="49" t="s">
+      <c r="B43" s="34"/>
+      <c r="C43" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="D43" s="9"/>
+      <c r="D43" s="8"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="n">
+      <c r="A44" s="5" t="n">
         <v>45704</v>
       </c>
-      <c r="B44" s="39" t="s">
+      <c r="B44" s="36" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D44" s="9"/>
+      <c r="D44" s="8"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="n">
+      <c r="A45" s="5" t="n">
         <v>46021</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C45" s="31"/>
-      <c r="D45" s="9"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="8"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="n">
+      <c r="A46" s="5" t="n">
         <v>46036</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="6" t="s">
         <v>63</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="9"/>
+      <c r="D46" s="8"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="n">
+      <c r="A47" s="5" t="n">
         <v>46155</v>
       </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="16" t="s">
+      <c r="B47" s="6"/>
+      <c r="C47" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="D47" s="9"/>
+      <c r="D47" s="8"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6" t="n">
+      <c r="A48" s="5" t="n">
         <v>46155</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="16" t="s">
+      <c r="B48" s="6"/>
+      <c r="C48" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="D48" s="9"/>
+      <c r="D48" s="8"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="n">
+      <c r="A49" s="5" t="n">
         <v>46204</v>
       </c>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7" t="s">
+      <c r="B49" s="6"/>
+      <c r="C49" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D49" s="9"/>
+      <c r="D49" s="8"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="21" t="n">
+      <c r="A50" s="20" t="n">
         <v>46288</v>
       </c>
-      <c r="B50" s="26" t="n">
+      <c r="B50" s="25" t="n">
         <v>0.375</v>
       </c>
-      <c r="C50" s="23" t="s">
+      <c r="C50" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D50" s="9"/>
-      <c r="F50" s="9"/>
+      <c r="D50" s="8"/>
+      <c r="F50" s="8"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="50"/>
-      <c r="B51" s="51"/>
-      <c r="C51" s="52" t="s">
+      <c r="A51" s="47"/>
+      <c r="B51" s="48"/>
+      <c r="C51" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="D51" s="9"/>
-      <c r="F51" s="9"/>
+      <c r="D51" s="8"/>
+      <c r="F51" s="8"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="50"/>
-      <c r="B52" s="51"/>
-      <c r="C52" s="53"/>
-      <c r="D52" s="9"/>
-      <c r="F52" s="9"/>
+      <c r="A52" s="47"/>
+      <c r="B52" s="48"/>
+      <c r="C52" s="50"/>
+      <c r="D52" s="8"/>
+      <c r="F52" s="8"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="50"/>
-      <c r="B53" s="51"/>
-      <c r="C53" s="53"/>
-      <c r="D53" s="9"/>
-      <c r="F53" s="9"/>
+      <c r="A53" s="47"/>
+      <c r="B53" s="48"/>
+      <c r="C53" s="50"/>
+      <c r="D53" s="8"/>
+      <c r="F53" s="8"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="7"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="54"/>
+      <c r="B54" s="6"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="6"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="10" t="n">
+      <c r="A55" s="9" t="n">
         <v>45475</v>
       </c>
-      <c r="B55" s="35" t="s">
+      <c r="B55" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="D55" s="32" t="n">
+      <c r="D55" s="31" t="n">
         <v>158437</v>
       </c>
-      <c r="E55" s="54"/>
+      <c r="E55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="33" t="n">
+      <c r="A56" s="32" t="n">
         <v>45482</v>
       </c>
-      <c r="B56" s="35"/>
-      <c r="C56" s="36" t="s">
+      <c r="B56" s="34"/>
+      <c r="C56" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="D56" s="32"/>
+      <c r="D56" s="31"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="35"/>
-      <c r="C57" s="49" t="s">
+      <c r="B57" s="34"/>
+      <c r="C57" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="D57" s="9"/>
+      <c r="D57" s="8"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6" t="n">
+      <c r="A58" s="5" t="n">
         <v>46069</v>
       </c>
-      <c r="B58" s="39" t="s">
+      <c r="B58" s="36" t="s">
         <v>87</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D58" s="9"/>
+      <c r="D58" s="8"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="7"/>
-      <c r="C59" s="16" t="s">
+      <c r="B59" s="6"/>
+      <c r="C59" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="D59" s="9"/>
+      <c r="D59" s="8"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6" t="n">
+      <c r="A60" s="5" t="n">
         <v>46077</v>
       </c>
-      <c r="B60" s="7"/>
+      <c r="B60" s="6"/>
       <c r="C60" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D60" s="9"/>
+      <c r="D60" s="8"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="7"/>
-      <c r="D61" s="9"/>
+      <c r="B61" s="6"/>
+      <c r="D61" s="8"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="55" t="n">
+      <c r="A62" s="51" t="n">
         <v>46175</v>
       </c>
-      <c r="B62" s="43" t="n">
+      <c r="B62" s="40" t="n">
         <v>0.413194444444444</v>
       </c>
-      <c r="C62" s="56" t="s">
+      <c r="C62" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="D62" s="57"/>
-      <c r="F62" s="8"/>
+      <c r="D62" s="7"/>
+      <c r="F62" s="7"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="7"/>
-      <c r="C63" s="7" t="s">
+      <c r="B63" s="6"/>
+      <c r="C63" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D63" s="9"/>
+      <c r="D63" s="8"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="58"/>
-      <c r="B64" s="59"/>
-      <c r="C64" s="60" t="s">
+      <c r="A64" s="52"/>
+      <c r="B64" s="53"/>
+      <c r="C64" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="D64" s="9"/>
+      <c r="D64" s="8"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="58"/>
-      <c r="B65" s="59"/>
-      <c r="C65" s="60" t="s">
+      <c r="A65" s="52"/>
+      <c r="B65" s="53"/>
+      <c r="C65" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="D65" s="9"/>
+      <c r="D65" s="8"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="58" t="n">
+      <c r="A66" s="52" t="n">
         <v>46252</v>
       </c>
-      <c r="B66" s="59"/>
-      <c r="C66" s="60" t="s">
+      <c r="B66" s="53"/>
+      <c r="C66" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="D66" s="9"/>
+      <c r="D66" s="8"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="58"/>
-      <c r="B67" s="59"/>
-      <c r="C67" s="61" t="s">
+      <c r="A67" s="52"/>
+      <c r="B67" s="53"/>
+      <c r="C67" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="D67" s="9"/>
+      <c r="D67" s="8"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="62" t="n">
+      <c r="A68" s="55" t="n">
         <v>46269</v>
       </c>
-      <c r="B68" s="63"/>
-      <c r="C68" s="64" t="s">
+      <c r="B68" s="56"/>
+      <c r="C68" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="D68" s="9"/>
+      <c r="D68" s="8"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="62"/>
-      <c r="B69" s="63"/>
-      <c r="C69" s="64" t="s">
+      <c r="A69" s="58"/>
+      <c r="B69" s="56"/>
+      <c r="C69" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="D69" s="9"/>
+      <c r="D69" s="8"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="58"/>
-      <c r="B70" s="59"/>
-      <c r="C70" s="60"/>
-      <c r="D70" s="9"/>
+      <c r="A70" s="52"/>
+      <c r="B70" s="53"/>
+      <c r="C70" s="54"/>
+      <c r="D70" s="8"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="58" t="n">
+      <c r="A71" s="52" t="n">
         <v>46259</v>
       </c>
-      <c r="B71" s="35" t="s">
+      <c r="B71" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="C71" s="65" t="s">
+      <c r="C71" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="D71" s="9"/>
+      <c r="D71" s="8"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="58"/>
-      <c r="B72" s="59"/>
-      <c r="C72" s="60"/>
-      <c r="D72" s="9"/>
+      <c r="A72" s="52"/>
+      <c r="B72" s="53"/>
+      <c r="C72" s="54"/>
+      <c r="D72" s="8"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="58"/>
-      <c r="B73" s="59"/>
-      <c r="C73" s="60"/>
-      <c r="D73" s="9"/>
+      <c r="A73" s="52"/>
+      <c r="B73" s="53"/>
+      <c r="C73" s="54"/>
+      <c r="D73" s="8"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="7"/>
-      <c r="C74" s="16"/>
-      <c r="D74" s="9"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="15"/>
+      <c r="D74" s="8"/>
     </row>
     <row r="75" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="10" t="n">
+      <c r="A75" s="9" t="n">
         <v>45342</v>
       </c>
-      <c r="B75" s="39" t="s">
+      <c r="B75" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="C75" s="24" t="s">
+      <c r="C75" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="D75" s="13" t="s">
+      <c r="D75" s="12" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="35"/>
-      <c r="C76" s="16" t="s">
+      <c r="B76" s="34"/>
+      <c r="C76" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="D76" s="9"/>
+      <c r="D76" s="8"/>
     </row>
     <row r="77" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="66" t="n">
+      <c r="A77" s="60" t="n">
         <v>45450</v>
       </c>
-      <c r="B77" s="39" t="s">
+      <c r="B77" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C77" s="6" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="6" t="n">
+      <c r="A78" s="5" t="n">
         <v>45680</v>
       </c>
-      <c r="B78" s="39"/>
-      <c r="C78" s="67" t="s">
+      <c r="B78" s="36"/>
+      <c r="C78" s="61" t="s">
         <v>105</v>
       </c>
       <c r="D78" s="1" t="s">
@@ -3916,668 +3868,661 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="35"/>
-      <c r="C79" s="7" t="s">
+      <c r="B79" s="34"/>
+      <c r="C79" s="6" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="6" t="n">
+      <c r="A80" s="5" t="n">
         <v>45726</v>
       </c>
-      <c r="B80" s="68"/>
+      <c r="B80" s="62"/>
       <c r="C80" s="1" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="69" t="n">
+      <c r="A81" s="63" t="n">
         <v>45765</v>
       </c>
-      <c r="B81" s="70" t="s">
+      <c r="B81" s="64" t="s">
         <v>109</v>
       </c>
-      <c r="C81" s="30" t="s">
+      <c r="C81" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="D81" s="9"/>
-      <c r="F81" s="9"/>
+      <c r="D81" s="8"/>
+      <c r="F81" s="8"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="71" t="n">
+      <c r="A82" s="65" t="n">
         <v>46195</v>
       </c>
-      <c r="B82" s="72" t="s">
+      <c r="B82" s="66" t="s">
         <v>111</v>
       </c>
-      <c r="C82" s="73" t="s">
+      <c r="C82" s="67" t="s">
         <v>112</v>
       </c>
-      <c r="D82" s="9"/>
-      <c r="F82" s="9"/>
+      <c r="D82" s="8"/>
+      <c r="F82" s="8"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="71"/>
-      <c r="B83" s="72"/>
-      <c r="C83" s="72" t="s">
+      <c r="A83" s="65"/>
+      <c r="B83" s="66"/>
+      <c r="C83" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="D83" s="38"/>
+      <c r="D83" s="8"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="6" t="n">
+      <c r="A84" s="5" t="n">
         <v>46204</v>
       </c>
-      <c r="B84" s="7" t="s">
+      <c r="B84" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C84" s="7" t="s">
+      <c r="C84" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D84" s="9"/>
+      <c r="D84" s="8"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="6" t="n">
+      <c r="A85" s="5" t="n">
         <v>46220</v>
       </c>
-      <c r="B85" s="0"/>
-      <c r="C85" s="0"/>
-      <c r="D85" s="9"/>
+      <c r="B85" s="1"/>
+      <c r="D85" s="8"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="6" t="n">
+      <c r="A86" s="5" t="n">
         <v>46329</v>
       </c>
-      <c r="B86" s="26" t="n">
+      <c r="B86" s="25" t="n">
         <v>0.420138888888889</v>
       </c>
-      <c r="C86" s="23" t="s">
+      <c r="C86" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D86" s="9"/>
+      <c r="D86" s="8"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0"/>
-      <c r="B87" s="7"/>
-      <c r="C87" s="74" t="s">
+      <c r="A87" s="1"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="68" t="s">
         <v>115</v>
       </c>
-      <c r="D87" s="9"/>
+      <c r="D87" s="8"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B88" s="7"/>
-      <c r="C88" s="74" t="s">
+      <c r="B88" s="6"/>
+      <c r="C88" s="68" t="s">
         <v>116</v>
       </c>
-      <c r="D88" s="9"/>
+      <c r="D88" s="8"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="7"/>
-      <c r="C89" s="25" t="s">
+      <c r="B89" s="6"/>
+      <c r="C89" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="D89" s="9"/>
+      <c r="D89" s="8"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="7"/>
-      <c r="C90" s="75" t="s">
+      <c r="B90" s="6"/>
+      <c r="C90" s="69" t="s">
         <v>118</v>
       </c>
-      <c r="D90" s="9"/>
+      <c r="D90" s="8"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="7"/>
-      <c r="C91" s="76" t="s">
+      <c r="B91" s="6"/>
+      <c r="C91" s="70" t="s">
         <v>119</v>
       </c>
-      <c r="D91" s="9"/>
+      <c r="D91" s="8"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="7"/>
-      <c r="C92" s="74"/>
-      <c r="D92" s="9"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="68"/>
+      <c r="D92" s="8"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="7"/>
-      <c r="C93" s="74"/>
-      <c r="D93" s="9"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="68"/>
+      <c r="D93" s="8"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="7"/>
-      <c r="C94" s="74"/>
-      <c r="D94" s="9"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="68"/>
+      <c r="D94" s="8"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B95" s="7"/>
-      <c r="C95" s="16"/>
-      <c r="D95" s="9"/>
+      <c r="B95" s="6"/>
+      <c r="C95" s="15"/>
+      <c r="D95" s="8"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="77" t="n">
+      <c r="A96" s="71" t="n">
         <v>46076</v>
       </c>
-      <c r="B96" s="78" t="s">
+      <c r="B96" s="72" t="s">
         <v>120</v>
       </c>
-      <c r="C96" s="78" t="s">
+      <c r="C96" s="72" t="s">
         <v>84</v>
       </c>
-      <c r="D96" s="23" t="n">
+      <c r="D96" s="22" t="n">
         <v>515608</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="77"/>
-      <c r="B97" s="7"/>
-      <c r="C97" s="78" t="s">
+      <c r="A97" s="71"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="72" t="s">
         <v>121</v>
       </c>
-      <c r="D97" s="79" t="n">
+      <c r="D97" s="73" t="n">
         <v>46088</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="77" t="n">
+      <c r="A98" s="71" t="n">
         <v>46120</v>
       </c>
-      <c r="B98" s="7" t="s">
+      <c r="B98" s="6" t="s">
         <v>122</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D98" s="80"/>
+      <c r="D98" s="74"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="77" t="n">
+      <c r="A99" s="71" t="n">
         <v>46121</v>
       </c>
-      <c r="B99" s="7" t="s">
+      <c r="B99" s="6" t="s">
         <v>124</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D99" s="80"/>
+      <c r="D99" s="74"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="77" t="n">
+      <c r="A100" s="71" t="n">
         <v>46120</v>
       </c>
-      <c r="B100" s="7" t="s">
+      <c r="B100" s="6" t="s">
         <v>122</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D100" s="80"/>
+      <c r="D100" s="74"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="77" t="n">
+      <c r="A101" s="71" t="n">
         <v>46121</v>
       </c>
-      <c r="B101" s="7" t="s">
+      <c r="B101" s="6" t="s">
         <v>124</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D101" s="80"/>
+      <c r="D101" s="74"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="77" t="n">
+      <c r="A102" s="71" t="n">
         <v>46121</v>
       </c>
-      <c r="B102" s="7"/>
+      <c r="B102" s="6"/>
       <c r="C102" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D102" s="80"/>
+      <c r="D102" s="74"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="77" t="n">
+      <c r="A103" s="71" t="n">
         <v>46122</v>
       </c>
-      <c r="B103" s="7"/>
+      <c r="B103" s="6"/>
       <c r="C103" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D103" s="80"/>
+      <c r="D103" s="74"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="77"/>
-      <c r="B104" s="7"/>
+      <c r="A104" s="71"/>
+      <c r="B104" s="6"/>
       <c r="C104" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D104" s="80"/>
+      <c r="D104" s="74"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="77"/>
-      <c r="B105" s="7"/>
+      <c r="A105" s="71"/>
+      <c r="B105" s="6"/>
       <c r="C105" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D105" s="80"/>
+      <c r="D105" s="74"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="77"/>
-      <c r="B106" s="7"/>
+      <c r="A106" s="71"/>
+      <c r="B106" s="6"/>
       <c r="C106" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D106" s="80"/>
+      <c r="D106" s="74"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="77"/>
-      <c r="B107" s="30"/>
-      <c r="C107" s="31" t="s">
+      <c r="A107" s="71"/>
+      <c r="B107" s="29"/>
+      <c r="C107" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="D107" s="80"/>
+      <c r="D107" s="74"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="77" t="n">
+      <c r="A108" s="71" t="n">
         <v>46122</v>
       </c>
-      <c r="B108" s="7" t="s">
+      <c r="B108" s="6" t="s">
         <v>106</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D108" s="8" t="s">
+      <c r="D108" s="7" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="77" t="n">
+      <c r="A109" s="71" t="n">
         <v>46122</v>
       </c>
-      <c r="B109" s="16" t="s">
+      <c r="B109" s="15" t="s">
         <v>106</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D109" s="81" t="s">
+      <c r="D109" s="75" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="77" t="n">
+      <c r="A110" s="71" t="n">
         <v>46127</v>
       </c>
-      <c r="B110" s="7"/>
-      <c r="C110" s="34" t="s">
+      <c r="B110" s="6"/>
+      <c r="C110" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="D110" s="82" t="n">
+      <c r="D110" s="22" t="n">
         <v>375000</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="77"/>
-      <c r="B111" s="7"/>
-      <c r="C111" s="34" t="s">
+      <c r="A111" s="71"/>
+      <c r="B111" s="6"/>
+      <c r="C111" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="D111" s="80"/>
+      <c r="D111" s="74"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="77"/>
-      <c r="B112" s="7"/>
+      <c r="A112" s="71"/>
+      <c r="B112" s="6"/>
       <c r="C112" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D112" s="80"/>
+      <c r="D112" s="74"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="80"/>
-      <c r="B113" s="83"/>
-      <c r="C113" s="83" t="s">
+      <c r="A113" s="74"/>
+      <c r="B113" s="76"/>
+      <c r="C113" s="76" t="s">
         <v>140</v>
       </c>
-      <c r="D113" s="80"/>
+      <c r="D113" s="74"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="77" t="n">
+      <c r="A114" s="71" t="n">
         <v>46206</v>
       </c>
-      <c r="B114" s="83"/>
-      <c r="C114" s="84" t="s">
+      <c r="B114" s="76"/>
+      <c r="C114" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="D114" s="80"/>
+      <c r="D114" s="74"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="77" t="n">
+      <c r="A115" s="71" t="n">
         <v>46126</v>
       </c>
-      <c r="B115" s="83"/>
-      <c r="C115" s="84" t="s">
+      <c r="B115" s="76"/>
+      <c r="C115" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="D115" s="80"/>
+      <c r="D115" s="74"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="77" t="n">
+      <c r="A116" s="71" t="n">
         <v>46217</v>
       </c>
-      <c r="B116" s="83"/>
-      <c r="C116" s="84" t="s">
+      <c r="B116" s="76"/>
+      <c r="C116" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="D116" s="80"/>
+      <c r="D116" s="74"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="80"/>
-      <c r="B117" s="83"/>
-      <c r="C117" s="84" t="s">
+      <c r="A117" s="74"/>
+      <c r="B117" s="76"/>
+      <c r="C117" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="D117" s="80"/>
-    </row>
-    <row r="118" s="88" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="85"/>
-      <c r="B118" s="86" t="s">
+      <c r="D117" s="74"/>
+    </row>
+    <row r="118" s="15" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="77"/>
+      <c r="B118" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C118" s="87" t="s">
+      <c r="C118" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D118" s="88" t="s">
+      <c r="D118" s="15" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="119" s="88" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="85"/>
-      <c r="C119" s="87" t="s">
+    <row r="119" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="77"/>
+      <c r="C119" s="6" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="120" s="88" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="85"/>
-      <c r="C120" s="87"/>
-    </row>
-    <row r="121" s="88" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="89" t="n">
+    <row r="120" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="77"/>
+      <c r="C120" s="6"/>
+    </row>
+    <row r="121" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="78" t="n">
         <v>46289</v>
       </c>
-      <c r="B121" s="26" t="n">
+      <c r="B121" s="25" t="n">
         <v>0.395833333333333</v>
       </c>
-      <c r="C121" s="87" t="s">
+      <c r="C121" s="6" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="7"/>
-      <c r="C122" s="16"/>
-      <c r="D122" s="9"/>
+      <c r="B122" s="6"/>
+      <c r="C122" s="15"/>
+      <c r="D122" s="8"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="77" t="n">
+      <c r="A123" s="71" t="n">
         <v>45676</v>
       </c>
-      <c r="B123" s="90" t="s">
+      <c r="B123" s="79" t="s">
         <v>149</v>
       </c>
-      <c r="C123" s="78" t="s">
+      <c r="C123" s="72" t="s">
         <v>150</v>
       </c>
-      <c r="D123" s="91"/>
+      <c r="D123" s="80"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="92" t="n">
+      <c r="A124" s="81" t="n">
         <v>45698</v>
       </c>
-      <c r="B124" s="7"/>
-      <c r="C124" s="34" t="s">
+      <c r="B124" s="6"/>
+      <c r="C124" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="D124" s="91"/>
+      <c r="D124" s="80"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="77"/>
-      <c r="B125" s="90"/>
-      <c r="C125" s="23" t="s">
+      <c r="A125" s="71"/>
+      <c r="B125" s="79"/>
+      <c r="C125" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="D125" s="93" t="s">
+      <c r="D125" s="82" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="94"/>
-      <c r="B126" s="95"/>
-      <c r="C126" s="53"/>
-      <c r="D126" s="96"/>
+      <c r="A126" s="83"/>
+      <c r="B126" s="84"/>
+      <c r="C126" s="50"/>
+      <c r="D126" s="85"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="94"/>
-      <c r="B127" s="95"/>
-      <c r="C127" s="52" t="s">
+      <c r="A127" s="83"/>
+      <c r="B127" s="84"/>
+      <c r="C127" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="D127" s="96"/>
+      <c r="D127" s="85"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="94"/>
-      <c r="B128" s="95"/>
-      <c r="C128" s="53"/>
-      <c r="D128" s="96"/>
+      <c r="A128" s="83"/>
+      <c r="B128" s="84"/>
+      <c r="C128" s="50"/>
+      <c r="D128" s="85"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="94"/>
-      <c r="B129" s="95"/>
-      <c r="C129" s="53"/>
-      <c r="D129" s="96"/>
+      <c r="A129" s="83"/>
+      <c r="B129" s="84"/>
+      <c r="C129" s="50"/>
+      <c r="D129" s="85"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="94"/>
-      <c r="B130" s="95"/>
-      <c r="C130" s="53"/>
-      <c r="D130" s="96"/>
+      <c r="A130" s="83"/>
+      <c r="B130" s="84"/>
+      <c r="C130" s="50"/>
+      <c r="D130" s="85"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B131" s="7"/>
-      <c r="C131" s="15"/>
-      <c r="D131" s="9"/>
+      <c r="B131" s="6"/>
+      <c r="C131" s="14"/>
+      <c r="D131" s="8"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="77" t="n">
+      <c r="A132" s="71" t="n">
         <v>46205</v>
       </c>
-      <c r="B132" s="90" t="s">
+      <c r="B132" s="79" t="s">
         <v>154</v>
       </c>
-      <c r="C132" s="78" t="s">
+      <c r="C132" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="D132" s="91"/>
+      <c r="D132" s="80"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="92" t="n">
+      <c r="A133" s="81" t="n">
         <v>45482</v>
       </c>
-      <c r="B133" s="7"/>
-      <c r="C133" s="34" t="s">
+      <c r="B133" s="6"/>
+      <c r="C133" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="D133" s="91"/>
+      <c r="D133" s="80"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="77" t="n">
+      <c r="A134" s="71" t="n">
         <v>45672</v>
       </c>
-      <c r="B134" s="90"/>
-      <c r="C134" s="78"/>
-      <c r="D134" s="93" t="s">
+      <c r="B134" s="79"/>
+      <c r="C134" s="72"/>
+      <c r="D134" s="82" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B135" s="7"/>
-      <c r="C135" s="16"/>
-      <c r="D135" s="9"/>
+      <c r="B135" s="6"/>
+      <c r="C135" s="15"/>
+      <c r="D135" s="8"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="97" t="n">
+      <c r="A136" s="86" t="n">
         <v>45588</v>
       </c>
-      <c r="B136" s="98" t="s">
+      <c r="B136" s="87" t="s">
         <v>157</v>
       </c>
-      <c r="C136" s="99" t="s">
+      <c r="C136" s="88" t="s">
         <v>155</v>
       </c>
-      <c r="D136" s="93" t="s">
+      <c r="D136" s="82" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="97"/>
-      <c r="B137" s="98"/>
-      <c r="C137" s="99" t="s">
+      <c r="A137" s="86"/>
+      <c r="B137" s="87"/>
+      <c r="C137" s="88" t="s">
         <v>158</v>
       </c>
-      <c r="D137" s="100"/>
+      <c r="D137" s="89"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="101" t="n">
+      <c r="A138" s="90" t="n">
         <v>45438</v>
       </c>
-      <c r="B138" s="102" t="s">
+      <c r="B138" s="91" t="s">
         <v>159</v>
       </c>
-      <c r="C138" s="103" t="s">
+      <c r="C138" s="92" t="s">
         <v>160</v>
       </c>
-      <c r="D138" s="81" t="s">
+      <c r="D138" s="75" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="101"/>
-      <c r="B139" s="102"/>
-      <c r="C139" s="103" t="s">
+      <c r="A139" s="90"/>
+      <c r="B139" s="91"/>
+      <c r="C139" s="92" t="s">
         <v>161</v>
       </c>
-      <c r="D139" s="91" t="n">
+      <c r="D139" s="80" t="n">
         <v>193500</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="101" t="n">
+      <c r="A140" s="90" t="n">
         <v>45288</v>
       </c>
-      <c r="B140" s="104" t="s">
+      <c r="B140" s="93" t="s">
         <v>162</v>
       </c>
-      <c r="C140" s="105" t="s">
+      <c r="C140" s="94" t="s">
         <v>163</v>
       </c>
-      <c r="D140" s="105" t="s">
+      <c r="D140" s="94" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="101"/>
-      <c r="B141" s="104"/>
-      <c r="C141" s="105" t="s">
+      <c r="A141" s="90"/>
+      <c r="B141" s="93"/>
+      <c r="C141" s="94" t="s">
         <v>158</v>
       </c>
-      <c r="D141" s="106"/>
+      <c r="D141" s="95"/>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="101" t="n">
+      <c r="A142" s="90" t="n">
         <v>45148</v>
       </c>
-      <c r="B142" s="104" t="s">
+      <c r="B142" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="C142" s="105" t="s">
+      <c r="C142" s="94" t="s">
         <v>165</v>
       </c>
-      <c r="D142" s="107" t="s">
+      <c r="D142" s="96" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="101"/>
-      <c r="B143" s="104"/>
-      <c r="C143" s="105"/>
-      <c r="D143" s="106"/>
+      <c r="A143" s="90"/>
+      <c r="B143" s="93"/>
+      <c r="C143" s="94"/>
+      <c r="D143" s="95"/>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="101" t="n">
+      <c r="A144" s="90" t="n">
         <v>44928</v>
       </c>
-      <c r="B144" s="104" t="s">
+      <c r="B144" s="93" t="s">
         <v>167</v>
       </c>
-      <c r="C144" s="105" t="s">
+      <c r="C144" s="94" t="s">
         <v>160</v>
       </c>
-      <c r="D144" s="91" t="n">
+      <c r="D144" s="80" t="n">
         <v>24316</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="101"/>
-      <c r="B145" s="104"/>
-      <c r="C145" s="105"/>
-      <c r="D145" s="81" t="s">
+      <c r="A145" s="90"/>
+      <c r="B145" s="93"/>
+      <c r="C145" s="94"/>
+      <c r="D145" s="75" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="101" t="n">
+      <c r="A146" s="90" t="n">
         <v>44333</v>
       </c>
-      <c r="B146" s="104" t="s">
+      <c r="B146" s="93" t="s">
         <v>168</v>
       </c>
-      <c r="C146" s="105" t="s">
+      <c r="C146" s="94" t="s">
         <v>169</v>
       </c>
-      <c r="D146" s="91"/>
+      <c r="D146" s="80"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="101"/>
-      <c r="B147" s="104"/>
-      <c r="C147" s="105"/>
-      <c r="D147" s="106"/>
+      <c r="A147" s="90"/>
+      <c r="B147" s="93"/>
+      <c r="C147" s="94"/>
+      <c r="D147" s="95"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B148" s="7"/>
-      <c r="D148" s="9"/>
+      <c r="B148" s="6"/>
+      <c r="D148" s="8"/>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B152" s="7"/>
-      <c r="D152" s="9"/>
+      <c r="B152" s="6"/>
+      <c r="D152" s="8"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B153" s="7"/>
-      <c r="D153" s="9"/>
+      <c r="B153" s="6"/>
+      <c r="D153" s="8"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B154" s="7"/>
-      <c r="D154" s="9"/>
+      <c r="B154" s="6"/>
+      <c r="D154" s="8"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B155" s="7"/>
-      <c r="D155" s="9"/>
+      <c r="B155" s="6"/>
+      <c r="D155" s="8"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1"/>
-    </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D159" s="1"/>
-    </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D165" s="1"/>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B178" s="1"/>
@@ -4628,90 +4573,90 @@
   <dimension ref="A3:F14"/>
   <sheetFormatPr defaultColWidth="10.14453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="10.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.57"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11" t="s">
+      <c r="A5" s="9"/>
+      <c r="B5" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="13"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C7" s="16"/>
+      <c r="C7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="5"/>
+      <c r="A8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="7"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="7"/>
-      <c r="D10" s="18"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="17"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D11" s="19"/>
+      <c r="D11" s="18"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="5"/>
+      <c r="A12" s="19"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="20" t="n">
         <v>46177</v>
       </c>
-      <c r="B13" s="22" t="n">
+      <c r="B13" s="21" t="n">
         <v>0.413194444444444</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="F13" s="5"/>
+      <c r="D13" s="4"/>
+      <c r="F13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="D14" s="4"/>
+      <c r="F14" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4732,104 +4677,104 @@
   <dimension ref="A3:F18"/>
   <sheetFormatPr defaultColWidth="10.14453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="10.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.57"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10"/>
-      <c r="B9" s="11" t="s">
+      <c r="A9" s="9"/>
+      <c r="B9" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="13"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E10" s="5"/>
+      <c r="E10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C11" s="16"/>
+      <c r="C11" s="15"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="5"/>
+      <c r="A12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="7"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="7"/>
-      <c r="D14" s="18"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="17"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="19"/>
+      <c r="D15" s="18"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="5"/>
+      <c r="A16" s="19"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="20" t="n">
         <v>46177</v>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B17" s="21" t="n">
         <v>0.413194444444444</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="F17" s="5"/>
+      <c r="D17" s="4"/>
+      <c r="F17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="D18" s="4"/>
+      <c r="F18" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4851,114 +4796,114 @@
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="108" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="97" width="10.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="6" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="5" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="13.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="5" width="13.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="98" t="s">
         <v>174</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="109"/>
-      <c r="B2" s="113" t="s">
+      <c r="A2" s="98"/>
+      <c r="B2" s="102" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="111" t="s">
+      <c r="C2" s="100" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="112"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="110"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="109"/>
-      <c r="B3" s="110"/>
-      <c r="C3" s="111"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
+      <c r="A3" s="98"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="109"/>
-      <c r="B4" s="114" t="s">
+      <c r="A4" s="98"/>
+      <c r="B4" s="103" t="s">
         <v>177</v>
       </c>
-      <c r="C4" s="111"/>
-      <c r="D4" s="113" t="s">
+      <c r="C4" s="100"/>
+      <c r="D4" s="102" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="113" t="s">
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="102" t="s">
         <v>179</v>
       </c>
-      <c r="H4" s="113" t="s">
+      <c r="H4" s="102" t="s">
         <v>180</v>
       </c>
-      <c r="I4" s="110"/>
+      <c r="I4" s="99"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="109"/>
-      <c r="B5" s="114" t="s">
+      <c r="A5" s="98"/>
+      <c r="B5" s="103" t="s">
         <v>177</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="D5" s="110" t="s">
+      <c r="D5" s="99" t="s">
         <v>181</v>
       </c>
-      <c r="E5" s="110"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="115" t="s">
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="104" t="s">
         <v>182</v>
       </c>
-      <c r="H5" s="113" t="s">
+      <c r="H5" s="102" t="s">
         <v>180</v>
       </c>
-      <c r="I5" s="110"/>
+      <c r="I5" s="99"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="109"/>
-      <c r="B6" s="110"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
-      <c r="G6" s="112"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="110"/>
+      <c r="A6" s="98"/>
+      <c r="B6" s="99"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="101"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="99"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="109"/>
-      <c r="B7" s="116" t="s">
+      <c r="A7" s="98"/>
+      <c r="B7" s="105" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="108" t="n">
+      <c r="C7" s="97" t="n">
         <v>45827</v>
       </c>
-      <c r="D7" s="111" t="s">
+      <c r="D7" s="100" t="s">
         <v>184</v>
       </c>
       <c r="E7" s="1" t="n">
@@ -4967,76 +4912,76 @@
       <c r="F7" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="H7" s="110" t="s">
+      <c r="H7" s="99" t="s">
         <v>185</v>
       </c>
-      <c r="I7" s="110"/>
+      <c r="I7" s="99"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="109"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="111"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
-      <c r="F8" s="110"/>
-      <c r="G8" s="112"/>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
+      <c r="A8" s="98"/>
+      <c r="B8" s="99"/>
+      <c r="C8" s="100"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="101"/>
+      <c r="H8" s="99"/>
+      <c r="I8" s="99"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="109"/>
-      <c r="B9" s="117" t="s">
+      <c r="A9" s="98"/>
+      <c r="B9" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="108" t="n">
+      <c r="C9" s="97" t="n">
         <v>45939</v>
       </c>
-      <c r="D9" s="118" t="s">
+      <c r="D9" s="107" t="s">
         <v>186</v>
       </c>
-      <c r="E9" s="118" t="n">
+      <c r="E9" s="107" t="n">
         <v>9</v>
       </c>
-      <c r="F9" s="118" t="n">
+      <c r="F9" s="107" t="n">
         <v>30</v>
       </c>
-      <c r="H9" s="110" t="s">
+      <c r="H9" s="99" t="s">
         <v>187</v>
       </c>
-      <c r="I9" s="110"/>
+      <c r="I9" s="99"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="109"/>
-      <c r="B10" s="117" t="s">
+      <c r="A10" s="98"/>
+      <c r="B10" s="106" t="s">
         <v>188</v>
       </c>
-      <c r="C10" s="111" t="n">
+      <c r="C10" s="100" t="n">
         <v>45939</v>
       </c>
-      <c r="D10" s="110" t="s">
+      <c r="D10" s="99" t="s">
         <v>181</v>
       </c>
-      <c r="E10" s="110" t="n">
+      <c r="E10" s="99" t="n">
         <v>9</v>
       </c>
-      <c r="F10" s="110" t="n">
+      <c r="F10" s="99" t="n">
         <v>40</v>
       </c>
-      <c r="G10" s="112"/>
-      <c r="H10" s="110" t="s">
+      <c r="G10" s="101"/>
+      <c r="H10" s="99" t="s">
         <v>187</v>
       </c>
-      <c r="I10" s="110"/>
+      <c r="I10" s="99"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="109"/>
-      <c r="B11" s="117" t="s">
+      <c r="A11" s="98"/>
+      <c r="B11" s="106" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="111" t="n">
+      <c r="C11" s="100" t="n">
         <v>45952</v>
       </c>
-      <c r="D11" s="110" t="s">
+      <c r="D11" s="99" t="s">
         <v>189</v>
       </c>
       <c r="E11" s="1" t="n">
@@ -5045,1516 +4990,1516 @@
       <c r="F11" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="G11" s="110"/>
-      <c r="H11" s="110" t="s">
+      <c r="G11" s="99"/>
+      <c r="H11" s="99" t="s">
         <v>190</v>
       </c>
-      <c r="I11" s="112"/>
+      <c r="I11" s="101"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="109"/>
-      <c r="B12" s="117" t="s">
+      <c r="A12" s="98"/>
+      <c r="B12" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="111" t="n">
+      <c r="C12" s="100" t="n">
         <v>45952</v>
       </c>
-      <c r="D12" s="110" t="s">
+      <c r="D12" s="99" t="s">
         <v>189</v>
       </c>
-      <c r="E12" s="110" t="n">
+      <c r="E12" s="99" t="n">
         <v>9</v>
       </c>
-      <c r="F12" s="110" t="n">
+      <c r="F12" s="99" t="n">
         <v>35</v>
       </c>
-      <c r="G12" s="112"/>
-      <c r="H12" s="110" t="s">
+      <c r="G12" s="101"/>
+      <c r="H12" s="99" t="s">
         <v>190</v>
       </c>
-      <c r="I12" s="112"/>
+      <c r="I12" s="101"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="109"/>
-      <c r="B13" s="118"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="110"/>
-      <c r="E13" s="110"/>
-      <c r="F13" s="110"/>
-      <c r="G13" s="112"/>
-      <c r="H13" s="110"/>
-      <c r="I13" s="112"/>
+      <c r="A13" s="98"/>
+      <c r="B13" s="107"/>
+      <c r="C13" s="100"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="101"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="101"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="109"/>
-      <c r="I14" s="110"/>
+      <c r="A14" s="98"/>
+      <c r="I14" s="99"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="109"/>
-      <c r="I15" s="110"/>
+      <c r="A15" s="98"/>
+      <c r="I15" s="99"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="119"/>
-      <c r="J16" s="16"/>
+      <c r="A16" s="108"/>
+      <c r="J16" s="15"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="120"/>
-      <c r="B17" s="121" t="s">
+      <c r="A17" s="109"/>
+      <c r="B17" s="110" t="s">
         <v>191</v>
       </c>
-      <c r="C17" s="122" t="s">
+      <c r="C17" s="111" t="s">
         <v>192</v>
       </c>
-      <c r="D17" s="121"/>
-      <c r="E17" s="123" t="s">
+      <c r="D17" s="110"/>
+      <c r="E17" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="123"/>
-      <c r="G17" s="124" t="s">
+      <c r="F17" s="112"/>
+      <c r="G17" s="113" t="s">
         <v>193</v>
       </c>
-      <c r="H17" s="121" t="s">
+      <c r="H17" s="110" t="s">
         <v>194</v>
       </c>
-      <c r="I17" s="121" t="s">
+      <c r="I17" s="110" t="s">
         <v>195</v>
       </c>
-      <c r="J17" s="125"/>
+      <c r="J17" s="114"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="59" t="s">
+      <c r="A18" s="53" t="s">
         <v>178</v>
       </c>
-      <c r="B18" s="126" t="s">
+      <c r="B18" s="115" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="127" t="n">
+      <c r="C18" s="116" t="n">
         <v>45342</v>
       </c>
-      <c r="D18" s="59" t="s">
+      <c r="D18" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="E18" s="128"/>
-      <c r="F18" s="129" t="s">
+      <c r="E18" s="117"/>
+      <c r="F18" s="118" t="s">
         <v>197</v>
       </c>
-      <c r="G18" s="58"/>
-      <c r="H18" s="128"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="125"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="114"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="59"/>
-      <c r="B19" s="130" t="s">
+      <c r="A19" s="53"/>
+      <c r="B19" s="119" t="s">
         <v>198</v>
       </c>
-      <c r="C19" s="127" t="n">
+      <c r="C19" s="116" t="n">
         <v>45537</v>
       </c>
-      <c r="D19" s="59" t="s">
+      <c r="D19" s="53" t="s">
         <v>199</v>
       </c>
-      <c r="E19" s="128"/>
-      <c r="F19" s="131" t="s">
+      <c r="E19" s="117"/>
+      <c r="F19" s="120" t="s">
         <v>200</v>
       </c>
-      <c r="G19" s="58" t="n">
+      <c r="G19" s="52" t="n">
         <v>45691</v>
       </c>
-      <c r="H19" s="128"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="125"/>
+      <c r="H19" s="117"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="114"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19"/>
-      <c r="B20" s="132"/>
-      <c r="C20" s="133"/>
-      <c r="D20" s="35" t="s">
+      <c r="A20" s="18"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="121"/>
+      <c r="D20" s="34" t="s">
         <v>201</v>
       </c>
-      <c r="F20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="J20" s="125"/>
+      <c r="F20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="J20" s="114"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7"/>
-      <c r="C21" s="134" t="n">
+      <c r="A21" s="6"/>
+      <c r="C21" s="122" t="n">
         <v>45726</v>
       </c>
-      <c r="D21" s="135" t="s">
+      <c r="D21" s="123" t="s">
         <v>202</v>
       </c>
-      <c r="E21" s="135"/>
-      <c r="F21" s="136"/>
-      <c r="G21" s="136"/>
-      <c r="H21" s="137"/>
-      <c r="I21" s="138"/>
-      <c r="J21" s="125"/>
+      <c r="E21" s="123"/>
+      <c r="F21" s="124"/>
+      <c r="G21" s="124"/>
+      <c r="H21" s="125"/>
+      <c r="I21" s="126"/>
+      <c r="J21" s="114"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7"/>
-      <c r="C22" s="139"/>
-      <c r="D22" s="140"/>
-      <c r="E22" s="140"/>
-      <c r="F22" s="141"/>
-      <c r="G22" s="141"/>
-      <c r="H22" s="112"/>
-      <c r="I22" s="112"/>
-      <c r="J22" s="125"/>
+      <c r="A22" s="6"/>
+      <c r="C22" s="127"/>
+      <c r="D22" s="128"/>
+      <c r="E22" s="128"/>
+      <c r="F22" s="129"/>
+      <c r="G22" s="129"/>
+      <c r="H22" s="101"/>
+      <c r="I22" s="101"/>
+      <c r="J22" s="114"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="119"/>
-      <c r="J23" s="125"/>
+      <c r="A23" s="108"/>
+      <c r="J23" s="114"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="142"/>
-      <c r="B24" s="125"/>
-      <c r="C24" s="143"/>
-      <c r="D24" s="125"/>
-      <c r="E24" s="125"/>
-      <c r="F24" s="125"/>
-      <c r="G24" s="144"/>
-      <c r="H24" s="125"/>
-      <c r="I24" s="125"/>
-      <c r="J24" s="125"/>
+      <c r="A24" s="130"/>
+      <c r="B24" s="114"/>
+      <c r="C24" s="131"/>
+      <c r="D24" s="114"/>
+      <c r="E24" s="114"/>
+      <c r="F24" s="114"/>
+      <c r="G24" s="132"/>
+      <c r="H24" s="114"/>
+      <c r="I24" s="114"/>
+      <c r="J24" s="114"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="119"/>
+      <c r="A25" s="108"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="119"/>
+      <c r="A26" s="108"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="145"/>
-      <c r="B27" s="146" t="s">
+      <c r="A27" s="133"/>
+      <c r="B27" s="134" t="s">
         <v>191</v>
       </c>
-      <c r="C27" s="147" t="s">
+      <c r="C27" s="135" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="146"/>
-      <c r="E27" s="148" t="s">
+      <c r="D27" s="134"/>
+      <c r="E27" s="136" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="148"/>
-      <c r="G27" s="149" t="s">
+      <c r="F27" s="136"/>
+      <c r="G27" s="137" t="s">
         <v>193</v>
       </c>
-      <c r="H27" s="146" t="s">
+      <c r="H27" s="134" t="s">
         <v>194</v>
       </c>
-      <c r="I27" s="146" t="s">
+      <c r="I27" s="134" t="s">
         <v>195</v>
       </c>
-      <c r="J27" s="150"/>
+      <c r="J27" s="138"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="119" t="s">
+      <c r="A28" s="108" t="s">
         <v>203</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="H28" s="151" t="s">
+      <c r="H28" s="139" t="s">
         <v>205</v>
       </c>
-      <c r="I28" s="152" t="n">
+      <c r="I28" s="140" t="n">
         <v>45712</v>
       </c>
-      <c r="J28" s="150"/>
+      <c r="J28" s="138"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="119"/>
-      <c r="J29" s="150"/>
+      <c r="A29" s="108"/>
+      <c r="J29" s="138"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7"/>
-      <c r="B30" s="16"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="153" t="s">
+      <c r="A30" s="6"/>
+      <c r="B30" s="15"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="141" t="s">
         <v>206</v>
       </c>
-      <c r="J30" s="150"/>
+      <c r="J30" s="138"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="154"/>
-      <c r="B31" s="150"/>
-      <c r="C31" s="155"/>
-      <c r="D31" s="154"/>
-      <c r="E31" s="154"/>
-      <c r="F31" s="154"/>
-      <c r="G31" s="156"/>
-      <c r="H31" s="154"/>
-      <c r="I31" s="156"/>
-      <c r="J31" s="150"/>
+      <c r="A31" s="142"/>
+      <c r="B31" s="138"/>
+      <c r="C31" s="143"/>
+      <c r="D31" s="142"/>
+      <c r="E31" s="142"/>
+      <c r="F31" s="142"/>
+      <c r="G31" s="144"/>
+      <c r="H31" s="142"/>
+      <c r="I31" s="144"/>
+      <c r="J31" s="138"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="119"/>
+      <c r="A32" s="108"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="119"/>
+      <c r="A33" s="108"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="157"/>
-      <c r="B34" s="158" t="s">
+      <c r="A34" s="145"/>
+      <c r="B34" s="146" t="s">
         <v>191</v>
       </c>
-      <c r="C34" s="159" t="s">
+      <c r="C34" s="147" t="s">
         <v>192</v>
       </c>
-      <c r="D34" s="158"/>
-      <c r="E34" s="160" t="s">
+      <c r="D34" s="146"/>
+      <c r="E34" s="148" t="s">
         <v>21</v>
       </c>
-      <c r="F34" s="160"/>
-      <c r="G34" s="161" t="s">
+      <c r="F34" s="148"/>
+      <c r="G34" s="149" t="s">
         <v>193</v>
       </c>
-      <c r="H34" s="158" t="s">
+      <c r="H34" s="146" t="s">
         <v>194</v>
       </c>
-      <c r="I34" s="158" t="s">
+      <c r="I34" s="146" t="s">
         <v>195</v>
       </c>
-      <c r="J34" s="125"/>
+      <c r="J34" s="114"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="154" t="s">
+      <c r="A35" s="142" t="s">
         <v>207</v>
       </c>
-      <c r="B35" s="126" t="s">
+      <c r="B35" s="115" t="s">
         <v>49</v>
       </c>
-      <c r="C35" s="143" t="n">
+      <c r="C35" s="131" t="n">
         <v>45475</v>
       </c>
-      <c r="D35" s="151" t="s">
+      <c r="D35" s="139" t="s">
         <v>208</v>
       </c>
-      <c r="E35" s="162" t="n">
+      <c r="E35" s="150" t="n">
         <v>97</v>
       </c>
-      <c r="F35" s="151" t="s">
+      <c r="F35" s="139" t="s">
         <v>197</v>
       </c>
-      <c r="H35" s="151" t="s">
+      <c r="H35" s="139" t="s">
         <v>209</v>
       </c>
-      <c r="I35" s="144" t="n">
+      <c r="I35" s="132" t="n">
         <v>45705</v>
       </c>
-      <c r="J35" s="125"/>
+      <c r="J35" s="114"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="151"/>
-      <c r="B36" s="163" t="s">
+      <c r="A36" s="139"/>
+      <c r="B36" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="C36" s="143" t="n">
+      <c r="C36" s="131" t="n">
         <v>45604</v>
       </c>
-      <c r="D36" s="151" t="s">
+      <c r="D36" s="139" t="s">
         <v>208</v>
       </c>
-      <c r="E36" s="162" t="n">
+      <c r="E36" s="150" t="n">
         <v>178</v>
       </c>
-      <c r="F36" s="151" t="s">
+      <c r="F36" s="139" t="s">
         <v>197</v>
       </c>
-      <c r="H36" s="95" t="s">
+      <c r="H36" s="84" t="s">
         <v>210</v>
       </c>
-      <c r="I36" s="164" t="n">
+      <c r="I36" s="152" t="n">
         <v>45705</v>
       </c>
-      <c r="J36" s="125"/>
+      <c r="J36" s="114"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7"/>
-      <c r="B37" s="165" t="s">
+      <c r="A37" s="6"/>
+      <c r="B37" s="153" t="s">
         <v>56</v>
       </c>
-      <c r="C37" s="108" t="n">
+      <c r="C37" s="97" t="n">
         <v>45704</v>
       </c>
-      <c r="D37" s="25" t="s">
+      <c r="D37" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="J37" s="125"/>
+      <c r="J37" s="114"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7" t="s">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C38" s="108" t="n">
+      <c r="C38" s="97" t="n">
         <v>45705</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="H38" s="7"/>
-      <c r="J38" s="125"/>
+      <c r="H38" s="6"/>
+      <c r="J38" s="114"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7"/>
-      <c r="C39" s="166"/>
-      <c r="D39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="J39" s="125"/>
+      <c r="A39" s="6"/>
+      <c r="C39" s="154"/>
+      <c r="D39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="J39" s="114"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7"/>
-      <c r="C40" s="166" t="s">
+      <c r="A40" s="6"/>
+      <c r="C40" s="154" t="s">
         <v>213</v>
       </c>
-      <c r="D40" s="25" t="s">
+      <c r="D40" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="H40" s="7"/>
-      <c r="J40" s="125"/>
+      <c r="H40" s="6"/>
+      <c r="J40" s="114"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7"/>
-      <c r="C41" s="167" t="n">
+      <c r="A41" s="6"/>
+      <c r="C41" s="155" t="n">
         <v>45717</v>
       </c>
-      <c r="D41" s="168" t="s">
+      <c r="D41" s="156" t="s">
         <v>19</v>
       </c>
-      <c r="E41" s="169" t="s">
+      <c r="E41" s="157" t="s">
         <v>215</v>
       </c>
-      <c r="F41" s="168"/>
-      <c r="G41" s="170"/>
-      <c r="H41" s="168" t="s">
+      <c r="F41" s="156"/>
+      <c r="G41" s="158"/>
+      <c r="H41" s="156" t="s">
         <v>216</v>
       </c>
-      <c r="I41" s="171" t="s">
+      <c r="I41" s="159" t="s">
         <v>217</v>
       </c>
-      <c r="J41" s="125"/>
+      <c r="J41" s="114"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7"/>
-      <c r="C42" s="172"/>
-      <c r="D42" s="7" t="s">
+      <c r="A42" s="6"/>
+      <c r="C42" s="160"/>
+      <c r="D42" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="H42" s="7" t="s">
+      <c r="H42" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="J42" s="125"/>
+      <c r="J42" s="114"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="173"/>
-      <c r="B43" s="174" t="s">
+      <c r="A43" s="161"/>
+      <c r="B43" s="162" t="s">
         <v>220</v>
       </c>
-      <c r="C43" s="175" t="n">
+      <c r="C43" s="163" t="n">
         <v>45805</v>
       </c>
-      <c r="D43" s="176" t="n">
+      <c r="D43" s="164" t="n">
         <v>0.409722222222222</v>
       </c>
-      <c r="E43" s="173" t="s">
+      <c r="E43" s="161" t="s">
         <v>221</v>
       </c>
-      <c r="F43" s="173"/>
-      <c r="G43" s="177"/>
-      <c r="H43" s="173"/>
-      <c r="I43" s="177"/>
-      <c r="J43" s="178"/>
+      <c r="F43" s="161"/>
+      <c r="G43" s="165"/>
+      <c r="H43" s="161"/>
+      <c r="I43" s="165"/>
+      <c r="J43" s="166"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="151"/>
-      <c r="B44" s="125"/>
-      <c r="C44" s="179" t="n">
+      <c r="A44" s="139"/>
+      <c r="B44" s="114"/>
+      <c r="C44" s="167" t="n">
         <v>45805</v>
       </c>
-      <c r="D44" s="162" t="s">
+      <c r="D44" s="150" t="s">
         <v>222</v>
       </c>
-      <c r="E44" s="162"/>
-      <c r="F44" s="162"/>
-      <c r="G44" s="180"/>
-      <c r="H44" s="125"/>
-      <c r="I44" s="144"/>
-      <c r="J44" s="125"/>
+      <c r="E44" s="150"/>
+      <c r="F44" s="150"/>
+      <c r="G44" s="168"/>
+      <c r="H44" s="114"/>
+      <c r="I44" s="132"/>
+      <c r="J44" s="114"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7"/>
+      <c r="A45" s="6"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7"/>
-      <c r="C46" s="166"/>
-      <c r="D46" s="7"/>
+      <c r="A46" s="6"/>
+      <c r="C46" s="154"/>
+      <c r="D46" s="6"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="157"/>
-      <c r="B47" s="158" t="s">
+      <c r="A47" s="145"/>
+      <c r="B47" s="146" t="s">
         <v>191</v>
       </c>
-      <c r="C47" s="159" t="s">
+      <c r="C47" s="147" t="s">
         <v>192</v>
       </c>
-      <c r="D47" s="158"/>
-      <c r="E47" s="160" t="s">
+      <c r="D47" s="146"/>
+      <c r="E47" s="148" t="s">
         <v>21</v>
       </c>
-      <c r="F47" s="160"/>
-      <c r="G47" s="161" t="s">
+      <c r="F47" s="148"/>
+      <c r="G47" s="149" t="s">
         <v>193</v>
       </c>
-      <c r="H47" s="158" t="s">
+      <c r="H47" s="146" t="s">
         <v>194</v>
       </c>
-      <c r="I47" s="158" t="s">
+      <c r="I47" s="146" t="s">
         <v>195</v>
       </c>
-      <c r="J47" s="125"/>
+      <c r="J47" s="114"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="151" t="s">
+      <c r="A48" s="139" t="s">
         <v>207</v>
       </c>
-      <c r="B48" s="126" t="s">
+      <c r="B48" s="115" t="s">
         <v>75</v>
       </c>
-      <c r="C48" s="181" t="n">
+      <c r="C48" s="169" t="n">
         <v>45588</v>
       </c>
-      <c r="D48" s="162" t="s">
+      <c r="D48" s="150" t="s">
         <v>223</v>
       </c>
-      <c r="E48" s="125"/>
-      <c r="F48" s="151" t="s">
+      <c r="E48" s="114"/>
+      <c r="F48" s="139" t="s">
         <v>197</v>
       </c>
-      <c r="H48" s="151" t="s">
+      <c r="H48" s="139" t="s">
         <v>224</v>
       </c>
-      <c r="I48" s="144" t="n">
+      <c r="I48" s="132" t="n">
         <v>45630</v>
       </c>
-      <c r="J48" s="125"/>
+      <c r="J48" s="114"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="151"/>
-      <c r="B49" s="126" t="s">
+      <c r="A49" s="139"/>
+      <c r="B49" s="115" t="s">
         <v>75</v>
       </c>
-      <c r="C49" s="143"/>
-      <c r="D49" s="151"/>
-      <c r="E49" s="125"/>
-      <c r="F49" s="151"/>
-      <c r="H49" s="95" t="s">
+      <c r="C49" s="131"/>
+      <c r="D49" s="139"/>
+      <c r="E49" s="114"/>
+      <c r="F49" s="139"/>
+      <c r="H49" s="84" t="s">
         <v>225</v>
       </c>
-      <c r="I49" s="144" t="n">
+      <c r="I49" s="132" t="n">
         <v>45630</v>
       </c>
-      <c r="J49" s="125"/>
+      <c r="J49" s="114"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="151"/>
-      <c r="B50" s="165" t="s">
+      <c r="A50" s="139"/>
+      <c r="B50" s="153" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="182" t="n">
+      <c r="C50" s="170" t="n">
         <v>45704</v>
       </c>
-      <c r="D50" s="25" t="s">
+      <c r="D50" s="24" t="s">
         <v>226</v>
       </c>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="J50" s="125"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="J50" s="114"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7"/>
-      <c r="B51" s="7" t="s">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C51" s="108" t="n">
+      <c r="C51" s="97" t="n">
         <v>45709</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="H51" s="7"/>
-      <c r="J51" s="125"/>
+      <c r="H51" s="6"/>
+      <c r="J51" s="114"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7"/>
-      <c r="C52" s="166" t="s">
+      <c r="A52" s="6"/>
+      <c r="C52" s="154" t="s">
         <v>213</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="H52" s="7"/>
-      <c r="J52" s="125"/>
+      <c r="H52" s="6"/>
+      <c r="J52" s="114"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7"/>
-      <c r="C53" s="166" t="n">
+      <c r="A53" s="6"/>
+      <c r="C53" s="154" t="n">
         <v>45712</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D53" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="H53" s="7"/>
-      <c r="J53" s="125"/>
+      <c r="H53" s="6"/>
+      <c r="J53" s="114"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7"/>
-      <c r="C54" s="183" t="n">
+      <c r="A54" s="6"/>
+      <c r="C54" s="171" t="n">
         <v>45717</v>
       </c>
-      <c r="D54" s="184" t="s">
+      <c r="D54" s="172" t="s">
         <v>19</v>
       </c>
-      <c r="E54" s="185" t="s">
+      <c r="E54" s="173" t="s">
         <v>215</v>
       </c>
-      <c r="F54" s="184"/>
-      <c r="G54" s="186"/>
-      <c r="H54" s="184" t="s">
+      <c r="F54" s="172"/>
+      <c r="G54" s="174"/>
+      <c r="H54" s="172" t="s">
         <v>216</v>
       </c>
-      <c r="I54" s="187"/>
-      <c r="J54" s="125"/>
+      <c r="I54" s="175"/>
+      <c r="J54" s="114"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7"/>
-      <c r="C55" s="7" t="s">
+      <c r="A55" s="6"/>
+      <c r="C55" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="F55" s="6"/>
-      <c r="G55" s="188"/>
-      <c r="H55" s="189"/>
-      <c r="I55" s="188"/>
-      <c r="J55" s="125"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="176"/>
+      <c r="H55" s="177"/>
+      <c r="I55" s="176"/>
+      <c r="J55" s="114"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="7"/>
-      <c r="C56" s="7" t="s">
+      <c r="A56" s="6"/>
+      <c r="C56" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="F56" s="6"/>
-      <c r="G56" s="188"/>
-      <c r="H56" s="189"/>
-      <c r="I56" s="190" t="s">
+      <c r="F56" s="5"/>
+      <c r="G56" s="176"/>
+      <c r="H56" s="177"/>
+      <c r="I56" s="178" t="s">
         <v>217</v>
       </c>
-      <c r="J56" s="125"/>
+      <c r="J56" s="114"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="7"/>
-      <c r="B57" s="191" t="s">
+      <c r="A57" s="6"/>
+      <c r="B57" s="179" t="s">
         <v>220</v>
       </c>
-      <c r="C57" s="192" t="n">
+      <c r="C57" s="180" t="n">
         <v>45805</v>
       </c>
-      <c r="D57" s="193" t="n">
+      <c r="D57" s="181" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="125"/>
+      <c r="J57" s="114"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="151"/>
-      <c r="B58" s="125"/>
-      <c r="C58" s="194" t="n">
+      <c r="A58" s="139"/>
+      <c r="B58" s="114"/>
+      <c r="C58" s="182" t="n">
         <v>45805</v>
       </c>
-      <c r="D58" s="151" t="s">
+      <c r="D58" s="139" t="s">
         <v>230</v>
       </c>
-      <c r="E58" s="125"/>
-      <c r="F58" s="125"/>
-      <c r="G58" s="144"/>
-      <c r="H58" s="125"/>
-      <c r="I58" s="144"/>
-      <c r="J58" s="125"/>
+      <c r="E58" s="114"/>
+      <c r="F58" s="114"/>
+      <c r="G58" s="132"/>
+      <c r="H58" s="114"/>
+      <c r="I58" s="132"/>
+      <c r="J58" s="114"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7"/>
-      <c r="B59" s="16"/>
-      <c r="C59" s="166"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="H59" s="16"/>
-      <c r="J59" s="16"/>
+      <c r="A59" s="6"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="154"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="15"/>
+      <c r="H59" s="15"/>
+      <c r="J59" s="15"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7"/>
-      <c r="B60" s="16"/>
-      <c r="C60" s="166"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-      <c r="H60" s="16"/>
-      <c r="J60" s="16"/>
+      <c r="A60" s="6"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="154"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="15"/>
+      <c r="H60" s="15"/>
+      <c r="J60" s="15"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-      <c r="H61" s="7"/>
+      <c r="A61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="H61" s="6"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="195"/>
-      <c r="B62" s="196" t="s">
+      <c r="A62" s="183"/>
+      <c r="B62" s="184" t="s">
         <v>191</v>
       </c>
-      <c r="C62" s="197" t="s">
+      <c r="C62" s="185" t="s">
         <v>192</v>
       </c>
-      <c r="D62" s="196"/>
-      <c r="E62" s="198" t="s">
+      <c r="D62" s="184"/>
+      <c r="E62" s="186" t="s">
         <v>21</v>
       </c>
-      <c r="F62" s="198"/>
-      <c r="G62" s="199" t="s">
+      <c r="F62" s="186"/>
+      <c r="G62" s="187" t="s">
         <v>193</v>
       </c>
-      <c r="H62" s="196" t="s">
+      <c r="H62" s="184" t="s">
         <v>194</v>
       </c>
-      <c r="I62" s="196" t="s">
+      <c r="I62" s="184" t="s">
         <v>195</v>
       </c>
-      <c r="J62" s="200"/>
+      <c r="J62" s="188"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="154" t="s">
+      <c r="A63" s="142" t="s">
         <v>231</v>
       </c>
-      <c r="B63" s="126" t="s">
+      <c r="B63" s="115" t="s">
         <v>83</v>
       </c>
-      <c r="C63" s="143" t="n">
+      <c r="C63" s="131" t="n">
         <v>45475</v>
       </c>
-      <c r="D63" s="151" t="s">
+      <c r="D63" s="139" t="s">
         <v>208</v>
       </c>
-      <c r="E63" s="162" t="n">
+      <c r="E63" s="150" t="n">
         <v>214</v>
       </c>
-      <c r="F63" s="151" t="s">
+      <c r="F63" s="139" t="s">
         <v>197</v>
       </c>
-      <c r="H63" s="151" t="s">
+      <c r="H63" s="139" t="s">
         <v>232</v>
       </c>
-      <c r="I63" s="144" t="n">
+      <c r="I63" s="132" t="n">
         <v>45702</v>
       </c>
-      <c r="J63" s="200"/>
+      <c r="J63" s="188"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="154"/>
-      <c r="B64" s="125"/>
-      <c r="C64" s="143"/>
-      <c r="D64" s="201" t="n">
+      <c r="A64" s="142"/>
+      <c r="B64" s="114"/>
+      <c r="C64" s="131"/>
+      <c r="D64" s="189" t="n">
         <v>158437</v>
       </c>
-      <c r="E64" s="125"/>
-      <c r="F64" s="151"/>
-      <c r="H64" s="95" t="s">
+      <c r="E64" s="114"/>
+      <c r="F64" s="139"/>
+      <c r="H64" s="84" t="s">
         <v>233</v>
       </c>
-      <c r="I64" s="144" t="n">
+      <c r="I64" s="132" t="n">
         <v>45702</v>
       </c>
-      <c r="J64" s="200"/>
+      <c r="J64" s="188"/>
     </row>
     <row r="65" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7"/>
-      <c r="B65" s="165" t="s">
+      <c r="A65" s="6"/>
+      <c r="B65" s="153" t="s">
         <v>87</v>
       </c>
-      <c r="C65" s="108" t="n">
+      <c r="C65" s="97" t="n">
         <v>45704</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="D65" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="H65" s="7"/>
-      <c r="J65" s="200"/>
+      <c r="H65" s="6"/>
+      <c r="J65" s="188"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7"/>
-      <c r="B66" s="7" t="s">
+      <c r="A66" s="6"/>
+      <c r="B66" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C66" s="108" t="n">
+      <c r="C66" s="97" t="n">
         <v>45705</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="D66" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="H66" s="7"/>
-      <c r="J66" s="200"/>
+      <c r="H66" s="6"/>
+      <c r="J66" s="188"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="7"/>
-      <c r="D67" s="7" t="s">
+      <c r="A67" s="6"/>
+      <c r="D67" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="H67" s="7"/>
-      <c r="J67" s="200"/>
+      <c r="H67" s="6"/>
+      <c r="J67" s="188"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="7"/>
-      <c r="C68" s="166" t="s">
+      <c r="A68" s="6"/>
+      <c r="C68" s="154" t="s">
         <v>213</v>
       </c>
-      <c r="D68" s="25" t="s">
+      <c r="D68" s="24" t="s">
         <v>237</v>
       </c>
-      <c r="H68" s="7"/>
-      <c r="J68" s="200"/>
+      <c r="H68" s="6"/>
+      <c r="J68" s="188"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="7"/>
-      <c r="C69" s="202" t="n">
+      <c r="A69" s="6"/>
+      <c r="C69" s="190" t="n">
         <v>45711</v>
       </c>
-      <c r="D69" s="203" t="s">
+      <c r="D69" s="191" t="s">
         <v>238</v>
       </c>
-      <c r="E69" s="203"/>
-      <c r="F69" s="203"/>
-      <c r="G69" s="204"/>
-      <c r="H69" s="203"/>
-      <c r="I69" s="205"/>
-      <c r="J69" s="200"/>
+      <c r="E69" s="191"/>
+      <c r="F69" s="191"/>
+      <c r="G69" s="192"/>
+      <c r="H69" s="191"/>
+      <c r="I69" s="193"/>
+      <c r="J69" s="188"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7" t="s">
+      <c r="A70" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B70" s="16"/>
-      <c r="C70" s="172" t="s">
+      <c r="B70" s="15"/>
+      <c r="C70" s="160" t="s">
         <v>239</v>
       </c>
-      <c r="D70" s="189"/>
-      <c r="E70" s="189"/>
-      <c r="F70" s="189"/>
-      <c r="G70" s="188"/>
-      <c r="H70" s="189"/>
-      <c r="I70" s="188"/>
-      <c r="J70" s="200"/>
+      <c r="D70" s="177"/>
+      <c r="E70" s="177"/>
+      <c r="F70" s="177"/>
+      <c r="G70" s="176"/>
+      <c r="H70" s="177"/>
+      <c r="I70" s="176"/>
+      <c r="J70" s="188"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7" t="n">
+      <c r="A71" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B71" s="16"/>
-      <c r="C71" s="172" t="s">
+      <c r="B71" s="15"/>
+      <c r="C71" s="160" t="s">
         <v>240</v>
       </c>
-      <c r="D71" s="25" t="s">
+      <c r="D71" s="24" t="s">
         <v>241</v>
       </c>
-      <c r="E71" s="189"/>
-      <c r="F71" s="189"/>
-      <c r="G71" s="188"/>
-      <c r="H71" s="189"/>
-      <c r="I71" s="188"/>
-      <c r="J71" s="200"/>
+      <c r="E71" s="177"/>
+      <c r="F71" s="177"/>
+      <c r="G71" s="176"/>
+      <c r="H71" s="177"/>
+      <c r="I71" s="176"/>
+      <c r="J71" s="188"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="7"/>
-      <c r="D72" s="7" t="s">
+      <c r="A72" s="6"/>
+      <c r="D72" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="H72" s="7"/>
-      <c r="I72" s="153" t="s">
+      <c r="H72" s="6"/>
+      <c r="I72" s="141" t="s">
         <v>243</v>
       </c>
-      <c r="J72" s="200"/>
+      <c r="J72" s="188"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="7"/>
-      <c r="C73" s="172"/>
-      <c r="D73" s="7" t="s">
+      <c r="A73" s="6"/>
+      <c r="C73" s="160"/>
+      <c r="D73" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="H73" s="7"/>
-      <c r="I73" s="153" t="s">
+      <c r="H73" s="6"/>
+      <c r="I73" s="141" t="s">
         <v>245</v>
       </c>
-      <c r="J73" s="200"/>
+      <c r="J73" s="188"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="7"/>
-      <c r="B74" s="174" t="s">
+      <c r="A74" s="6"/>
+      <c r="B74" s="162" t="s">
         <v>220</v>
       </c>
-      <c r="C74" s="206" t="n">
+      <c r="C74" s="194" t="n">
         <v>45792</v>
       </c>
-      <c r="D74" s="176" t="n">
+      <c r="D74" s="164" t="n">
         <v>0.399305555555556</v>
       </c>
-      <c r="E74" s="16"/>
-      <c r="F74" s="16"/>
-      <c r="J74" s="200"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="15"/>
+      <c r="J74" s="188"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="207"/>
-      <c r="B75" s="208" t="s">
+      <c r="A75" s="195"/>
+      <c r="B75" s="196" t="s">
         <v>63</v>
       </c>
-      <c r="C75" s="209" t="n">
+      <c r="C75" s="197" t="n">
         <v>45939</v>
       </c>
-      <c r="D75" s="210" t="n">
+      <c r="D75" s="198" t="n">
         <v>0.402777777777778</v>
       </c>
-      <c r="E75" s="211"/>
-      <c r="F75" s="211"/>
-      <c r="G75" s="212" t="s">
+      <c r="E75" s="199"/>
+      <c r="F75" s="199"/>
+      <c r="G75" s="200" t="s">
         <v>246</v>
       </c>
-      <c r="H75" s="212" t="s">
+      <c r="H75" s="200" t="s">
         <v>247</v>
       </c>
-      <c r="I75" s="212" t="s">
+      <c r="I75" s="200" t="s">
         <v>248</v>
       </c>
-      <c r="J75" s="200"/>
+      <c r="J75" s="188"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="7"/>
-      <c r="C76" s="166"/>
-      <c r="D76" s="7"/>
-      <c r="H76" s="7"/>
+      <c r="A76" s="6"/>
+      <c r="C76" s="154"/>
+      <c r="D76" s="6"/>
+      <c r="H76" s="6"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7"/>
-      <c r="C77" s="166"/>
-      <c r="D77" s="7"/>
-      <c r="H77" s="7"/>
+      <c r="A77" s="6"/>
+      <c r="C77" s="154"/>
+      <c r="D77" s="6"/>
+      <c r="H77" s="6"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="213"/>
-      <c r="B78" s="214" t="s">
+      <c r="A78" s="201"/>
+      <c r="B78" s="202" t="s">
         <v>191</v>
       </c>
-      <c r="C78" s="215" t="s">
+      <c r="C78" s="203" t="s">
         <v>192</v>
       </c>
-      <c r="D78" s="214"/>
-      <c r="E78" s="216" t="s">
+      <c r="D78" s="202"/>
+      <c r="E78" s="204" t="s">
         <v>21</v>
       </c>
-      <c r="F78" s="216"/>
-      <c r="G78" s="217" t="s">
+      <c r="F78" s="204"/>
+      <c r="G78" s="205" t="s">
         <v>193</v>
       </c>
-      <c r="H78" s="214" t="s">
+      <c r="H78" s="202" t="s">
         <v>194</v>
       </c>
-      <c r="I78" s="214" t="s">
+      <c r="I78" s="202" t="s">
         <v>195</v>
       </c>
-      <c r="J78" s="150"/>
+      <c r="J78" s="138"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="151" t="s">
+      <c r="A79" s="139" t="s">
         <v>231</v>
       </c>
-      <c r="B79" s="126" t="s">
+      <c r="B79" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="C79" s="143" t="n">
+      <c r="C79" s="131" t="n">
         <v>45676</v>
       </c>
-      <c r="D79" s="162" t="s">
+      <c r="D79" s="150" t="s">
         <v>223</v>
       </c>
-      <c r="E79" s="151"/>
-      <c r="F79" s="151" t="s">
+      <c r="E79" s="139"/>
+      <c r="F79" s="139" t="s">
         <v>197</v>
       </c>
-      <c r="H79" s="7" t="s">
+      <c r="H79" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="J79" s="150"/>
+      <c r="J79" s="138"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="151" t="s">
+      <c r="A80" s="139" t="s">
         <v>231</v>
       </c>
-      <c r="B80" s="126" t="s">
+      <c r="B80" s="115" t="s">
         <v>149</v>
       </c>
-      <c r="C80" s="143"/>
-      <c r="D80" s="151"/>
-      <c r="E80" s="151"/>
-      <c r="F80" s="151"/>
-      <c r="H80" s="95" t="s">
+      <c r="C80" s="131"/>
+      <c r="D80" s="139"/>
+      <c r="E80" s="139"/>
+      <c r="F80" s="139"/>
+      <c r="H80" s="84" t="s">
         <v>250</v>
       </c>
-      <c r="I80" s="218" t="n">
+      <c r="I80" s="206" t="n">
         <v>45714</v>
       </c>
-      <c r="J80" s="150"/>
+      <c r="J80" s="138"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="7"/>
-      <c r="B81" s="16"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
-      <c r="H81" s="7"/>
-      <c r="J81" s="150"/>
+      <c r="A81" s="6"/>
+      <c r="B81" s="15"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="J81" s="138"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="7"/>
-      <c r="B82" s="16"/>
-      <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
-      <c r="H82" s="7"/>
-      <c r="I82" s="153" t="s">
+      <c r="A82" s="6"/>
+      <c r="B82" s="15"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="141" t="s">
         <v>206</v>
       </c>
-      <c r="J82" s="150"/>
+      <c r="J82" s="138"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="154"/>
-      <c r="B83" s="150"/>
-      <c r="C83" s="155"/>
-      <c r="D83" s="154"/>
-      <c r="E83" s="154"/>
-      <c r="F83" s="154"/>
-      <c r="G83" s="156"/>
-      <c r="H83" s="154"/>
-      <c r="I83" s="156"/>
-      <c r="J83" s="150"/>
+      <c r="A83" s="142"/>
+      <c r="B83" s="138"/>
+      <c r="C83" s="143"/>
+      <c r="D83" s="142"/>
+      <c r="E83" s="142"/>
+      <c r="F83" s="142"/>
+      <c r="G83" s="144"/>
+      <c r="H83" s="142"/>
+      <c r="I83" s="144"/>
+      <c r="J83" s="138"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="7"/>
-      <c r="C84" s="166"/>
-      <c r="D84" s="7"/>
-      <c r="H84" s="7"/>
+      <c r="A84" s="6"/>
+      <c r="C84" s="154"/>
+      <c r="D84" s="6"/>
+      <c r="H84" s="6"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="7"/>
-      <c r="C85" s="166"/>
-      <c r="D85" s="7"/>
-      <c r="H85" s="7"/>
+      <c r="A85" s="6"/>
+      <c r="C85" s="154"/>
+      <c r="D85" s="6"/>
+      <c r="H85" s="6"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="195"/>
-      <c r="B86" s="196" t="s">
+      <c r="A86" s="183"/>
+      <c r="B86" s="184" t="s">
         <v>191</v>
       </c>
-      <c r="C86" s="197" t="s">
+      <c r="C86" s="185" t="s">
         <v>192</v>
       </c>
-      <c r="D86" s="196"/>
-      <c r="E86" s="198" t="s">
+      <c r="D86" s="184"/>
+      <c r="E86" s="186" t="s">
         <v>21</v>
       </c>
-      <c r="F86" s="198"/>
-      <c r="G86" s="199" t="s">
+      <c r="F86" s="186"/>
+      <c r="G86" s="187" t="s">
         <v>193</v>
       </c>
-      <c r="H86" s="196" t="s">
+      <c r="H86" s="184" t="s">
         <v>194</v>
       </c>
-      <c r="I86" s="196" t="s">
+      <c r="I86" s="184" t="s">
         <v>195</v>
       </c>
-      <c r="J86" s="200"/>
+      <c r="J86" s="188"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="151" t="s">
+      <c r="A87" s="139" t="s">
         <v>251</v>
       </c>
-      <c r="B87" s="126" t="s">
+      <c r="B87" s="115" t="s">
         <v>64</v>
       </c>
-      <c r="C87" s="219" t="n">
+      <c r="C87" s="207" t="n">
         <v>45603</v>
       </c>
-      <c r="D87" s="151" t="s">
+      <c r="D87" s="139" t="s">
         <v>208</v>
       </c>
-      <c r="E87" s="162" t="n">
+      <c r="E87" s="150" t="n">
         <v>156000</v>
       </c>
-      <c r="F87" s="151" t="s">
+      <c r="F87" s="139" t="s">
         <v>197</v>
       </c>
-      <c r="G87" s="144"/>
-      <c r="H87" s="7" t="s">
+      <c r="G87" s="132"/>
+      <c r="H87" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="I87" s="6" t="n">
+      <c r="I87" s="5" t="n">
         <v>45705</v>
       </c>
-      <c r="J87" s="200"/>
+      <c r="J87" s="188"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="151"/>
-      <c r="B88" s="125"/>
-      <c r="C88" s="143"/>
-      <c r="D88" s="151"/>
-      <c r="E88" s="125"/>
-      <c r="F88" s="151"/>
-      <c r="G88" s="144"/>
-      <c r="H88" s="95" t="s">
+      <c r="A88" s="139"/>
+      <c r="B88" s="114"/>
+      <c r="C88" s="131"/>
+      <c r="D88" s="139"/>
+      <c r="E88" s="114"/>
+      <c r="F88" s="139"/>
+      <c r="G88" s="132"/>
+      <c r="H88" s="84" t="s">
         <v>253</v>
       </c>
-      <c r="I88" s="6" t="n">
+      <c r="I88" s="5" t="n">
         <v>45705</v>
       </c>
-      <c r="J88" s="200"/>
+      <c r="J88" s="188"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="7"/>
-      <c r="B89" s="165" t="s">
+      <c r="A89" s="6"/>
+      <c r="B89" s="153" t="s">
         <v>254</v>
       </c>
-      <c r="C89" s="182" t="n">
+      <c r="C89" s="170" t="n">
         <v>45704</v>
       </c>
-      <c r="D89" s="7" t="s">
+      <c r="D89" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="F89" s="7"/>
-      <c r="H89" s="7"/>
-      <c r="J89" s="200"/>
+      <c r="F89" s="6"/>
+      <c r="H89" s="6"/>
+      <c r="J89" s="188"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="7"/>
-      <c r="B90" s="7" t="s">
+      <c r="A90" s="6"/>
+      <c r="B90" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C90" s="108" t="n">
+      <c r="C90" s="97" t="n">
         <v>45705</v>
       </c>
-      <c r="D90" s="7" t="s">
+      <c r="D90" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="H90" s="7"/>
-      <c r="J90" s="200"/>
+      <c r="H90" s="6"/>
+      <c r="J90" s="188"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="7"/>
-      <c r="J91" s="200"/>
+      <c r="A91" s="6"/>
+      <c r="J91" s="188"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="7"/>
-      <c r="C92" s="166" t="s">
+      <c r="A92" s="6"/>
+      <c r="C92" s="154" t="s">
         <v>213</v>
       </c>
-      <c r="D92" s="25" t="s">
+      <c r="D92" s="24" t="s">
         <v>237</v>
       </c>
-      <c r="G92" s="220"/>
-      <c r="H92" s="7"/>
-      <c r="J92" s="200"/>
+      <c r="G92" s="208"/>
+      <c r="H92" s="6"/>
+      <c r="J92" s="188"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="7"/>
-      <c r="C93" s="166" t="n">
+      <c r="A93" s="6"/>
+      <c r="C93" s="154" t="n">
         <v>45706</v>
       </c>
-      <c r="D93" s="7" t="s">
+      <c r="D93" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="H93" s="7"/>
-      <c r="J93" s="200"/>
+      <c r="H93" s="6"/>
+      <c r="J93" s="188"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="7"/>
-      <c r="C94" s="221" t="n">
+      <c r="A94" s="6"/>
+      <c r="C94" s="209" t="n">
         <v>45711</v>
       </c>
-      <c r="D94" s="184" t="s">
+      <c r="D94" s="172" t="s">
         <v>238</v>
       </c>
-      <c r="E94" s="184"/>
-      <c r="F94" s="184"/>
-      <c r="G94" s="186"/>
-      <c r="H94" s="184"/>
-      <c r="I94" s="187"/>
-      <c r="J94" s="200"/>
+      <c r="E94" s="172"/>
+      <c r="F94" s="172"/>
+      <c r="G94" s="174"/>
+      <c r="H94" s="172"/>
+      <c r="I94" s="175"/>
+      <c r="J94" s="188"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="7"/>
-      <c r="B95" s="7" t="s">
+      <c r="A95" s="6"/>
+      <c r="B95" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="C95" s="222"/>
-      <c r="D95" s="7" t="s">
+      <c r="C95" s="210"/>
+      <c r="D95" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="H95" s="7"/>
-      <c r="J95" s="200"/>
+      <c r="H95" s="6"/>
+      <c r="J95" s="188"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="7"/>
-      <c r="D96" s="7" t="s">
+      <c r="A96" s="6"/>
+      <c r="D96" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="H96" s="7"/>
-      <c r="J96" s="200"/>
+      <c r="H96" s="6"/>
+      <c r="J96" s="188"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="7"/>
-      <c r="D97" s="7"/>
-      <c r="H97" s="7"/>
-      <c r="I97" s="153" t="s">
+      <c r="A97" s="6"/>
+      <c r="D97" s="6"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="141" t="s">
         <v>259</v>
       </c>
-      <c r="J97" s="200"/>
+      <c r="J97" s="188"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="7"/>
-      <c r="D98" s="7"/>
-      <c r="H98" s="7"/>
-      <c r="I98" s="153" t="s">
+      <c r="A98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="141" t="s">
         <v>243</v>
       </c>
-      <c r="J98" s="200"/>
+      <c r="J98" s="188"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="223" t="s">
+      <c r="B99" s="211" t="s">
         <v>220</v>
       </c>
-      <c r="C99" s="224" t="n">
+      <c r="C99" s="212" t="n">
         <v>45792</v>
       </c>
-      <c r="D99" s="225" t="n">
+      <c r="D99" s="213" t="n">
         <v>0.395833333333333</v>
       </c>
-      <c r="E99" s="16"/>
-      <c r="F99" s="16" t="s">
+      <c r="E99" s="15"/>
+      <c r="F99" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="H99" s="16"/>
-      <c r="I99" s="16"/>
-      <c r="J99" s="200"/>
+      <c r="H99" s="15"/>
+      <c r="I99" s="15"/>
+      <c r="J99" s="188"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="200"/>
-      <c r="B100" s="226" t="s">
+      <c r="A100" s="188"/>
+      <c r="B100" s="214" t="s">
         <v>63</v>
       </c>
-      <c r="C100" s="227" t="n">
+      <c r="C100" s="215" t="n">
         <v>45939</v>
       </c>
-      <c r="D100" s="228" t="n">
+      <c r="D100" s="216" t="n">
         <v>0.395833333333333</v>
       </c>
-      <c r="E100" s="200"/>
-      <c r="F100" s="200"/>
-      <c r="G100" s="229"/>
-      <c r="H100" s="200"/>
-      <c r="I100" s="200"/>
-      <c r="J100" s="200"/>
+      <c r="E100" s="188"/>
+      <c r="F100" s="188"/>
+      <c r="G100" s="217"/>
+      <c r="H100" s="188"/>
+      <c r="I100" s="188"/>
+      <c r="J100" s="188"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="118"/>
-      <c r="B101" s="230"/>
-      <c r="C101" s="231"/>
-      <c r="D101" s="232"/>
-      <c r="E101" s="118"/>
-      <c r="F101" s="118"/>
-      <c r="G101" s="112"/>
-      <c r="H101" s="118"/>
-      <c r="I101" s="118"/>
-      <c r="J101" s="118"/>
+      <c r="A101" s="107"/>
+      <c r="B101" s="218"/>
+      <c r="C101" s="219"/>
+      <c r="D101" s="220"/>
+      <c r="E101" s="107"/>
+      <c r="F101" s="107"/>
+      <c r="G101" s="101"/>
+      <c r="H101" s="107"/>
+      <c r="I101" s="107"/>
+      <c r="J101" s="107"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="118"/>
-      <c r="B102" s="230"/>
-      <c r="C102" s="231"/>
-      <c r="D102" s="232"/>
-      <c r="E102" s="118"/>
-      <c r="F102" s="118"/>
-      <c r="G102" s="112"/>
-      <c r="H102" s="118"/>
-      <c r="I102" s="118"/>
-      <c r="J102" s="118"/>
+      <c r="A102" s="107"/>
+      <c r="B102" s="218"/>
+      <c r="C102" s="219"/>
+      <c r="D102" s="220"/>
+      <c r="E102" s="107"/>
+      <c r="F102" s="107"/>
+      <c r="G102" s="101"/>
+      <c r="H102" s="107"/>
+      <c r="I102" s="107"/>
+      <c r="J102" s="107"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="233"/>
-      <c r="B103" s="233"/>
-      <c r="C103" s="234"/>
-      <c r="D103" s="233"/>
-      <c r="E103" s="233"/>
-      <c r="F103" s="233"/>
-      <c r="G103" s="235"/>
-      <c r="H103" s="233"/>
-      <c r="I103" s="235"/>
+      <c r="A103" s="221"/>
+      <c r="B103" s="221"/>
+      <c r="C103" s="222"/>
+      <c r="D103" s="221"/>
+      <c r="E103" s="221"/>
+      <c r="F103" s="221"/>
+      <c r="G103" s="223"/>
+      <c r="H103" s="221"/>
+      <c r="I103" s="223"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="59" t="s">
+      <c r="A104" s="53" t="s">
         <v>251</v>
       </c>
-      <c r="B104" s="126" t="s">
+      <c r="B104" s="115" t="s">
         <v>157</v>
       </c>
-      <c r="C104" s="127" t="n">
+      <c r="C104" s="116" t="n">
         <v>45588</v>
       </c>
-      <c r="D104" s="59" t="s">
+      <c r="D104" s="53" t="s">
         <v>223</v>
       </c>
-      <c r="E104" s="128"/>
-      <c r="F104" s="128"/>
-      <c r="G104" s="236" t="n">
+      <c r="E104" s="117"/>
+      <c r="F104" s="117"/>
+      <c r="G104" s="224" t="n">
         <v>45672</v>
       </c>
-      <c r="H104" s="59" t="s">
+      <c r="H104" s="53" t="s">
         <v>261</v>
       </c>
-      <c r="I104" s="58" t="n">
+      <c r="I104" s="52" t="n">
         <v>45625</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="59"/>
-      <c r="B105" s="126" t="s">
+      <c r="A105" s="53"/>
+      <c r="B105" s="115" t="s">
         <v>262</v>
       </c>
-      <c r="C105" s="127"/>
-      <c r="D105" s="59"/>
-      <c r="E105" s="128"/>
-      <c r="F105" s="128"/>
-      <c r="G105" s="236"/>
-      <c r="H105" s="59"/>
-      <c r="I105" s="58"/>
+      <c r="C105" s="116"/>
+      <c r="D105" s="53"/>
+      <c r="E105" s="117"/>
+      <c r="F105" s="117"/>
+      <c r="G105" s="224"/>
+      <c r="H105" s="53"/>
+      <c r="I105" s="52"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="59" t="s">
+      <c r="A106" s="53" t="s">
         <v>251</v>
       </c>
-      <c r="B106" s="126" t="s">
+      <c r="B106" s="115" t="s">
         <v>157</v>
       </c>
-      <c r="C106" s="127" t="n">
+      <c r="C106" s="116" t="n">
         <v>45588</v>
       </c>
-      <c r="D106" s="59" t="s">
+      <c r="D106" s="53" t="s">
         <v>223</v>
       </c>
-      <c r="E106" s="128"/>
-      <c r="F106" s="128"/>
-      <c r="G106" s="236" t="n">
+      <c r="E106" s="117"/>
+      <c r="F106" s="117"/>
+      <c r="G106" s="224" t="n">
         <v>45672</v>
       </c>
-      <c r="H106" s="237" t="s">
+      <c r="H106" s="225" t="s">
         <v>263</v>
       </c>
-      <c r="I106" s="58" t="n">
+      <c r="I106" s="52" t="n">
         <v>45625</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="95" t="s">
+      <c r="A107" s="84" t="s">
         <v>251</v>
       </c>
-      <c r="B107" s="126" t="s">
+      <c r="B107" s="115" t="s">
         <v>154</v>
       </c>
-      <c r="C107" s="238" t="n">
+      <c r="C107" s="226" t="n">
         <v>45475</v>
       </c>
-      <c r="D107" s="95" t="s">
+      <c r="D107" s="84" t="s">
         <v>208</v>
       </c>
-      <c r="E107" s="239" t="n">
+      <c r="E107" s="227" t="n">
         <v>113</v>
       </c>
-      <c r="F107" s="95" t="s">
+      <c r="F107" s="84" t="s">
         <v>197</v>
       </c>
-      <c r="G107" s="236" t="n">
+      <c r="G107" s="224" t="n">
         <v>45672</v>
       </c>
-      <c r="H107" s="95" t="s">
+      <c r="H107" s="84" t="s">
         <v>252</v>
       </c>
-      <c r="I107" s="94" t="n">
+      <c r="I107" s="83" t="n">
         <v>45705</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="95"/>
-      <c r="B108" s="126" t="s">
+      <c r="A108" s="84"/>
+      <c r="B108" s="115" t="s">
         <v>264</v>
       </c>
-      <c r="C108" s="238"/>
-      <c r="D108" s="95"/>
-      <c r="E108" s="239"/>
-      <c r="F108" s="95"/>
-      <c r="G108" s="236"/>
-      <c r="H108" s="95"/>
-      <c r="I108" s="94"/>
+      <c r="C108" s="226"/>
+      <c r="D108" s="84"/>
+      <c r="E108" s="227"/>
+      <c r="F108" s="84"/>
+      <c r="G108" s="224"/>
+      <c r="H108" s="84"/>
+      <c r="I108" s="83"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="95" t="s">
+      <c r="A109" s="84" t="s">
         <v>251</v>
       </c>
-      <c r="B109" s="126" t="s">
+      <c r="B109" s="115" t="s">
         <v>154</v>
       </c>
-      <c r="C109" s="238"/>
-      <c r="D109" s="95" t="s">
+      <c r="C109" s="226"/>
+      <c r="D109" s="84" t="s">
         <v>208</v>
       </c>
-      <c r="E109" s="239" t="n">
+      <c r="E109" s="227" t="n">
         <v>113</v>
       </c>
-      <c r="F109" s="95" t="s">
+      <c r="F109" s="84" t="s">
         <v>197</v>
       </c>
-      <c r="G109" s="236" t="n">
+      <c r="G109" s="224" t="n">
         <v>45672</v>
       </c>
-      <c r="H109" s="240" t="s">
+      <c r="H109" s="228" t="s">
         <v>253</v>
       </c>
-      <c r="I109" s="94" t="n">
+      <c r="I109" s="83" t="n">
         <v>45705</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="241"/>
-      <c r="B113" s="233"/>
-      <c r="C113" s="234"/>
-      <c r="D113" s="241"/>
-      <c r="E113" s="233"/>
-      <c r="F113" s="235"/>
-      <c r="G113" s="235"/>
-      <c r="H113" s="235"/>
-      <c r="I113" s="235"/>
+      <c r="A113" s="229"/>
+      <c r="B113" s="221"/>
+      <c r="C113" s="222"/>
+      <c r="D113" s="229"/>
+      <c r="E113" s="221"/>
+      <c r="F113" s="223"/>
+      <c r="G113" s="223"/>
+      <c r="H113" s="223"/>
+      <c r="I113" s="223"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="59" t="s">
+      <c r="A114" s="53" t="s">
         <v>265</v>
       </c>
-      <c r="B114" s="207" t="s">
+      <c r="B114" s="195" t="s">
         <v>159</v>
       </c>
-      <c r="C114" s="242" t="n">
+      <c r="C114" s="230" t="n">
         <v>45438</v>
       </c>
-      <c r="D114" s="59" t="s">
+      <c r="D114" s="53" t="s">
         <v>208</v>
       </c>
-      <c r="E114" s="59" t="n">
+      <c r="E114" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="F114" s="243" t="s">
+      <c r="F114" s="231" t="s">
         <v>266</v>
       </c>
-      <c r="G114" s="129"/>
-      <c r="H114" s="59" t="s">
+      <c r="G114" s="118"/>
+      <c r="H114" s="53" t="s">
         <v>267</v>
       </c>
-      <c r="I114" s="129"/>
+      <c r="I114" s="118"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="59"/>
-      <c r="B115" s="244" t="s">
+      <c r="A115" s="53"/>
+      <c r="B115" s="232" t="s">
         <v>268</v>
       </c>
-      <c r="C115" s="245" t="n">
+      <c r="C115" s="233" t="n">
         <v>45486</v>
       </c>
-      <c r="D115" s="59" t="s">
+      <c r="D115" s="53" t="s">
         <v>269</v>
       </c>
-      <c r="E115" s="59"/>
-      <c r="F115" s="246" t="s">
+      <c r="E115" s="53"/>
+      <c r="F115" s="234" t="s">
         <v>266</v>
       </c>
-      <c r="G115" s="247" t="n">
+      <c r="G115" s="235" t="n">
         <v>45588</v>
       </c>
-      <c r="H115" s="59" t="s">
+      <c r="H115" s="53" t="s">
         <v>270</v>
       </c>
-      <c r="I115" s="129"/>
+      <c r="I115" s="118"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="59"/>
-      <c r="B116" s="244" t="s">
+      <c r="A116" s="53"/>
+      <c r="B116" s="232" t="s">
         <v>271</v>
       </c>
-      <c r="C116" s="245" t="n">
+      <c r="C116" s="233" t="n">
         <v>45590</v>
       </c>
-      <c r="D116" s="59" t="s">
+      <c r="D116" s="53" t="s">
         <v>201</v>
       </c>
-      <c r="E116" s="59"/>
-      <c r="F116" s="246" t="s">
+      <c r="E116" s="53"/>
+      <c r="F116" s="234" t="s">
         <v>266</v>
       </c>
-      <c r="G116" s="247" t="n">
+      <c r="G116" s="235" t="n">
         <v>45688</v>
       </c>
-      <c r="H116" s="59" t="s">
+      <c r="H116" s="53" t="s">
         <v>272</v>
       </c>
-      <c r="I116" s="129"/>
+      <c r="I116" s="118"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="59"/>
-      <c r="B117" s="248"/>
-      <c r="C117" s="249"/>
-      <c r="D117" s="248" t="s">
+      <c r="A117" s="53"/>
+      <c r="B117" s="236"/>
+      <c r="C117" s="237"/>
+      <c r="D117" s="236" t="s">
         <v>273</v>
       </c>
-      <c r="E117" s="248"/>
-      <c r="F117" s="250"/>
-      <c r="G117" s="251" t="n">
+      <c r="E117" s="236"/>
+      <c r="F117" s="238"/>
+      <c r="G117" s="239" t="n">
         <v>45782</v>
       </c>
-      <c r="H117" s="59" t="s">
+      <c r="H117" s="53" t="s">
         <v>274</v>
       </c>
-      <c r="I117" s="129"/>
+      <c r="I117" s="118"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="7"/>
-      <c r="B118" s="252"/>
-      <c r="C118" s="253"/>
-      <c r="D118" s="7"/>
-      <c r="E118" s="252"/>
-      <c r="F118" s="254"/>
-      <c r="G118" s="255"/>
+      <c r="A118" s="6"/>
+      <c r="B118" s="240"/>
+      <c r="C118" s="241"/>
+      <c r="D118" s="6"/>
+      <c r="E118" s="240"/>
+      <c r="F118" s="242"/>
+      <c r="G118" s="243"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="7"/>
-      <c r="B119" s="252"/>
-      <c r="C119" s="253"/>
-      <c r="D119" s="7"/>
-      <c r="E119" s="252"/>
-      <c r="F119" s="254"/>
-      <c r="G119" s="255"/>
+      <c r="A119" s="6"/>
+      <c r="B119" s="240"/>
+      <c r="C119" s="241"/>
+      <c r="D119" s="6"/>
+      <c r="E119" s="240"/>
+      <c r="F119" s="242"/>
+      <c r="G119" s="243"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6575,12 +6520,12 @@
   <dimension ref="A4:G15"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="9.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.14"/>
   </cols>
   <sheetData>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="n">
+      <c r="A4" s="5" t="n">
         <v>45967</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -6594,7 +6539,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="5" t="n">
         <v>45927</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -6608,56 +6553,56 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="5" t="n">
         <v>45708</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="6" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="5" t="n">
         <v>46064</v>
       </c>
-      <c r="E8" s="256" t="n">
+      <c r="E8" s="3" t="n">
         <v>0.416666666666667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="5" t="n">
         <v>46028</v>
       </c>
-      <c r="E15" s="256" t="n">
+      <c r="E15" s="3" t="n">
         <v>0.427083333333333</v>
       </c>
     </row>
